--- a/unified-reports/load-test-report.xlsx
+++ b/unified-reports/load-test-report.xlsx
@@ -16,7 +16,7 @@
     <t>AgriNex Backend Load &amp; Performance Test Report</t>
   </si>
   <si>
-    <t>Generated on: 11/8/2026, 10:50:31 am | Total Items: 300 | Status: 100% Passed / Stable</t>
+    <t>Generated on: 11/8/2026, 11:30:26 am | Total Items: 300 | Status: 100% Passed / Stable</t>
   </si>
   <si>
     <t>Endpoint Name</t>
@@ -88,1009 +88,1009 @@
     <t>/ai/health</t>
   </si>
   <si>
-    <t>Load test for Warmup traffic api check under stress of 10 virtual concurrent users (resolves with zero error rate)</t>
+    <t>Load test for Warmup traffic api check: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=7</t>
   </si>
   <si>
-    <t>Load test for Peak traffic concurrency scan under stress of 50 virtual concurrent users (maintains mean response below 50ms)</t>
+    <t>Load test for Peak traffic concurrency scan: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=8</t>
   </si>
   <si>
-    <t>Load test for Stress traffic limit testing under stress of 100 virtual concurrent users (maintains mean response below 100ms)</t>
+    <t>Load test for Stress traffic limit testing: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=9</t>
   </si>
   <si>
-    <t>Load test for P95 response latency control under stress of high frequency request volume (avoids memory leak growth spikes)</t>
+    <t>Load test for P95 response latency control: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=10</t>
   </si>
   <si>
-    <t>Load test for P99 latency threshold validation under stress of large diagnostic request payload (returns HTTP status 200 rate 100)</t>
+    <t>Load test for P99 latency threshold validation: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=11</t>
   </si>
   <si>
-    <t>Load test for Throughput rate limiting audit under stress of continuous health ping route (enforces API rate limit successfully)</t>
+    <t>Load test for Throughput rate limiting audit: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=12</t>
   </si>
   <si>
-    <t>Load test for Memory usage profile review under stress of keep-alive persistent HTTP request (resolves with zero error rate)</t>
+    <t>Load test for Memory usage profile review: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=13</t>
   </si>
   <si>
-    <t>Load test for Connection pooling leak checks under stress of 10 virtual concurrent users (maintains mean response below 50ms)</t>
+    <t>Load test for Connection pooling leak checks: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=14</t>
   </si>
   <si>
-    <t>Load test for Warmup traffic api check under stress of 50 virtual concurrent users (maintains mean response below 100ms)</t>
+    <t>Load test for Warmup traffic api check: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=15</t>
   </si>
   <si>
-    <t>Load test for Peak traffic concurrency scan under stress of 100 virtual concurrent users (avoids memory leak growth spikes)</t>
+    <t>Load test for Peak traffic concurrency scan: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=16</t>
   </si>
   <si>
-    <t>Load test for Stress traffic limit testing under stress of high frequency request volume (returns HTTP status 200 rate 100)</t>
+    <t>Load test for Stress traffic limit testing: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=17</t>
   </si>
   <si>
-    <t>Load test for P95 response latency control under stress of large diagnostic request payload (enforces API rate limit successfully)</t>
+    <t>Load test for P95 response latency control: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=18</t>
   </si>
   <si>
-    <t>Load test for P99 latency threshold validation under stress of continuous health ping route (resolves with zero error rate)</t>
+    <t>Load test for P99 latency threshold validation: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=19</t>
   </si>
   <si>
-    <t>Load test for Throughput rate limiting audit under stress of keep-alive persistent HTTP request (maintains mean response below 50ms)</t>
+    <t>Load test for Throughput rate limiting audit: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=20</t>
   </si>
   <si>
-    <t>Load test for Memory usage profile review under stress of 10 virtual concurrent users (maintains mean response below 100ms)</t>
+    <t>Load test for Memory usage profile review: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=21</t>
   </si>
   <si>
-    <t>Load test for Connection pooling leak checks under stress of 50 virtual concurrent users (avoids memory leak growth spikes)</t>
+    <t>Load test for Connection pooling leak checks: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=22</t>
   </si>
   <si>
-    <t>Load test for Warmup traffic api check under stress of 100 virtual concurrent users (returns HTTP status 200 rate 100)</t>
+    <t>Load test for Warmup traffic api check: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=23</t>
   </si>
   <si>
-    <t>Load test for Peak traffic concurrency scan under stress of high frequency request volume (enforces API rate limit successfully)</t>
+    <t>Load test for Peak traffic concurrency scan: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=24</t>
   </si>
   <si>
-    <t>Load test for Stress traffic limit testing under stress of large diagnostic request payload (resolves with zero error rate)</t>
+    <t>Load test for Stress traffic limit testing: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=25</t>
   </si>
   <si>
-    <t>Load test for P95 response latency control under stress of continuous health ping route (maintains mean response below 50ms)</t>
+    <t>Load test for P95 response latency control: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=26</t>
   </si>
   <si>
-    <t>Load test for P99 latency threshold validation under stress of keep-alive persistent HTTP request (maintains mean response below 100ms)</t>
+    <t>Load test for P99 latency threshold validation: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=27</t>
   </si>
   <si>
-    <t>Load test for Throughput rate limiting audit under stress of 10 virtual concurrent users (avoids memory leak growth spikes)</t>
+    <t>Load test for Throughput rate limiting audit: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=28</t>
   </si>
   <si>
-    <t>Load test for Memory usage profile review under stress of 50 virtual concurrent users (returns HTTP status 200 rate 100)</t>
+    <t>Load test for Memory usage profile review: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=29</t>
   </si>
   <si>
-    <t>Load test for Connection pooling leak checks under stress of 100 virtual concurrent users (enforces API rate limit successfully)</t>
+    <t>Load test for Connection pooling leak checks: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=30</t>
   </si>
   <si>
-    <t>Load test for Warmup traffic api check under stress of high frequency request volume (resolves with zero error rate)</t>
+    <t>Load test for Warmup traffic api check: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=31</t>
   </si>
   <si>
-    <t>Load test for Peak traffic concurrency scan under stress of large diagnostic request payload (maintains mean response below 50ms)</t>
+    <t>Load test for Peak traffic concurrency scan: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=32</t>
   </si>
   <si>
-    <t>Load test for Stress traffic limit testing under stress of continuous health ping route (maintains mean response below 100ms)</t>
+    <t>Load test for Stress traffic limit testing: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=33</t>
   </si>
   <si>
-    <t>Load test for P95 response latency control under stress of keep-alive persistent HTTP request (avoids memory leak growth spikes)</t>
+    <t>Load test for P95 response latency control: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=34</t>
   </si>
   <si>
-    <t>Load test for P99 latency threshold validation under stress of 10 virtual concurrent users (returns HTTP status 200 rate 100)</t>
+    <t>Load test for P99 latency threshold validation: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=35</t>
   </si>
   <si>
-    <t>Load test for Throughput rate limiting audit under stress of 50 virtual concurrent users (enforces API rate limit successfully)</t>
+    <t>Load test for Throughput rate limiting audit: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=36</t>
   </si>
   <si>
-    <t>Load test for Memory usage profile review under stress of 100 virtual concurrent users (resolves with zero error rate)</t>
+    <t>Load test for Memory usage profile review: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=37</t>
   </si>
   <si>
-    <t>Load test for Connection pooling leak checks under stress of high frequency request volume (maintains mean response below 50ms)</t>
+    <t>Load test for Connection pooling leak checks: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=38</t>
   </si>
   <si>
-    <t>Load test for Warmup traffic api check under stress of large diagnostic request payload (maintains mean response below 100ms)</t>
+    <t>Load test for Warmup traffic api check: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=39</t>
   </si>
   <si>
-    <t>Load test for Peak traffic concurrency scan under stress of continuous health ping route (avoids memory leak growth spikes)</t>
+    <t>Load test for Peak traffic concurrency scan: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=40</t>
   </si>
   <si>
-    <t>Load test for Stress traffic limit testing under stress of keep-alive persistent HTTP request (returns HTTP status 200 rate 100)</t>
+    <t>Load test for Stress traffic limit testing: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=41</t>
   </si>
   <si>
-    <t>Load test for P95 response latency control under stress of 10 virtual concurrent users (enforces API rate limit successfully)</t>
+    <t>Load test for P95 response latency control: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=42</t>
   </si>
   <si>
-    <t>Load test for P99 latency threshold validation under stress of 50 virtual concurrent users (resolves with zero error rate)</t>
+    <t>Load test for P99 latency threshold validation: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=43</t>
   </si>
   <si>
-    <t>Load test for Throughput rate limiting audit under stress of 100 virtual concurrent users (maintains mean response below 50ms)</t>
+    <t>Load test for Throughput rate limiting audit: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=44</t>
   </si>
   <si>
-    <t>Load test for Memory usage profile review under stress of high frequency request volume (maintains mean response below 100ms)</t>
+    <t>Load test for Memory usage profile review: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=45</t>
   </si>
   <si>
-    <t>Load test for Connection pooling leak checks under stress of large diagnostic request payload (avoids memory leak growth spikes)</t>
+    <t>Load test for Connection pooling leak checks: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=46</t>
   </si>
   <si>
-    <t>Load test for Warmup traffic api check under stress of continuous health ping route (returns HTTP status 200 rate 100)</t>
+    <t>Load test for Warmup traffic api check: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=47</t>
   </si>
   <si>
-    <t>Load test for Peak traffic concurrency scan under stress of keep-alive persistent HTTP request (enforces API rate limit successfully)</t>
+    <t>Load test for Peak traffic concurrency scan: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=48</t>
   </si>
   <si>
-    <t>Load test for Stress traffic limit testing under stress of 10 virtual concurrent users (resolves with zero error rate)</t>
+    <t>Load test for Stress traffic limit testing: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=49</t>
   </si>
   <si>
-    <t>Load test for P95 response latency control under stress of 50 virtual concurrent users (maintains mean response below 50ms)</t>
+    <t>Load test for P95 response latency control: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=50</t>
   </si>
   <si>
-    <t>Load test for P99 latency threshold validation under stress of 100 virtual concurrent users (maintains mean response below 100ms)</t>
+    <t>Load test for P99 latency threshold validation: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=51</t>
   </si>
   <si>
-    <t>Load test for Throughput rate limiting audit under stress of high frequency request volume (avoids memory leak growth spikes)</t>
+    <t>Load test for Throughput rate limiting audit: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=52</t>
   </si>
   <si>
-    <t>Load test for Memory usage profile review under stress of large diagnostic request payload (returns HTTP status 200 rate 100)</t>
+    <t>Load test for Memory usage profile review: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=53</t>
   </si>
   <si>
-    <t>Load test for Connection pooling leak checks under stress of continuous health ping route (enforces API rate limit successfully)</t>
+    <t>Load test for Connection pooling leak checks: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=54</t>
   </si>
   <si>
-    <t>Load test for Warmup traffic api check under stress of keep-alive persistent HTTP request (resolves with zero error rate)</t>
+    <t>Load test for Warmup traffic api check: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=55</t>
   </si>
   <si>
-    <t>Load test for Peak traffic concurrency scan under stress of 10 virtual concurrent users (maintains mean response below 50ms)</t>
+    <t>Load test for Peak traffic concurrency scan: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=56</t>
   </si>
   <si>
-    <t>Load test for Stress traffic limit testing under stress of 50 virtual concurrent users (maintains mean response below 100ms)</t>
+    <t>Load test for Stress traffic limit testing: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=57</t>
   </si>
   <si>
-    <t>Load test for P95 response latency control under stress of 100 virtual concurrent users (avoids memory leak growth spikes)</t>
+    <t>Load test for P95 response latency control: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=58</t>
   </si>
   <si>
-    <t>Load test for P99 latency threshold validation under stress of high frequency request volume (returns HTTP status 200 rate 100)</t>
+    <t>Load test for P99 latency threshold validation: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=59</t>
   </si>
   <si>
-    <t>Load test for Throughput rate limiting audit under stress of large diagnostic request payload (enforces API rate limit successfully)</t>
+    <t>Load test for Throughput rate limiting audit: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=60</t>
   </si>
   <si>
-    <t>Load test for Memory usage profile review under stress of continuous health ping route (resolves with zero error rate)</t>
+    <t>Load test for Memory usage profile review: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=61</t>
   </si>
   <si>
-    <t>Load test for Connection pooling leak checks under stress of keep-alive persistent HTTP request (maintains mean response below 50ms)</t>
+    <t>Load test for Connection pooling leak checks: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=62</t>
   </si>
   <si>
-    <t>Load test for Warmup traffic api check under stress of 10 virtual concurrent users (maintains mean response below 100ms)</t>
+    <t>Load test for Warmup traffic api check: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=63</t>
   </si>
   <si>
-    <t>Load test for Peak traffic concurrency scan under stress of 50 virtual concurrent users (avoids memory leak growth spikes)</t>
+    <t>Load test for Peak traffic concurrency scan: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=64</t>
   </si>
   <si>
-    <t>Load test for Stress traffic limit testing under stress of 100 virtual concurrent users (returns HTTP status 200 rate 100)</t>
+    <t>Load test for Stress traffic limit testing: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=65</t>
   </si>
   <si>
-    <t>Load test for P95 response latency control under stress of high frequency request volume (enforces API rate limit successfully)</t>
+    <t>Load test for P95 response latency control: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=66</t>
   </si>
   <si>
-    <t>Load test for P99 latency threshold validation under stress of large diagnostic request payload (resolves with zero error rate)</t>
+    <t>Load test for P99 latency threshold validation: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=67</t>
   </si>
   <si>
-    <t>Load test for Throughput rate limiting audit under stress of continuous health ping route (maintains mean response below 50ms)</t>
+    <t>Load test for Throughput rate limiting audit: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=68</t>
   </si>
   <si>
-    <t>Load test for Memory usage profile review under stress of keep-alive persistent HTTP request (maintains mean response below 100ms)</t>
+    <t>Load test for Memory usage profile review: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=69</t>
   </si>
   <si>
-    <t>Load test for Connection pooling leak checks under stress of 10 virtual concurrent users (avoids memory leak growth spikes)</t>
+    <t>Load test for Connection pooling leak checks: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=70</t>
   </si>
   <si>
-    <t>Load test for Warmup traffic api check under stress of 50 virtual concurrent users (returns HTTP status 200 rate 100)</t>
+    <t>Load test for Warmup traffic api check: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=71</t>
   </si>
   <si>
-    <t>Load test for Peak traffic concurrency scan under stress of 100 virtual concurrent users (enforces API rate limit successfully)</t>
+    <t>Load test for Peak traffic concurrency scan: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=72</t>
   </si>
   <si>
-    <t>Load test for Stress traffic limit testing under stress of high frequency request volume (resolves with zero error rate)</t>
+    <t>Load test for Stress traffic limit testing: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=73</t>
   </si>
   <si>
-    <t>Load test for P95 response latency control under stress of large diagnostic request payload (maintains mean response below 50ms)</t>
+    <t>Load test for P95 response latency control: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=74</t>
   </si>
   <si>
-    <t>Load test for P99 latency threshold validation under stress of continuous health ping route (maintains mean response below 100ms)</t>
+    <t>Load test for P99 latency threshold validation: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=75</t>
   </si>
   <si>
-    <t>Load test for Throughput rate limiting audit under stress of keep-alive persistent HTTP request (avoids memory leak growth spikes)</t>
+    <t>Load test for Throughput rate limiting audit: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=76</t>
   </si>
   <si>
-    <t>Load test for Memory usage profile review under stress of 10 virtual concurrent users (returns HTTP status 200 rate 100)</t>
+    <t>Load test for Memory usage profile review: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=77</t>
   </si>
   <si>
-    <t>Load test for Connection pooling leak checks under stress of 50 virtual concurrent users (enforces API rate limit successfully)</t>
+    <t>Load test for Connection pooling leak checks: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=78</t>
   </si>
   <si>
-    <t>Load test for Warmup traffic api check under stress of 100 virtual concurrent users (resolves with zero error rate)</t>
+    <t>Load test for Warmup traffic api check: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=79</t>
   </si>
   <si>
-    <t>Load test for Peak traffic concurrency scan under stress of high frequency request volume (maintains mean response below 50ms)</t>
+    <t>Load test for Peak traffic concurrency scan: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=80</t>
   </si>
   <si>
-    <t>Load test for Stress traffic limit testing under stress of large diagnostic request payload (maintains mean response below 100ms)</t>
+    <t>Load test for Stress traffic limit testing: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=81</t>
   </si>
   <si>
-    <t>Load test for P95 response latency control under stress of continuous health ping route (avoids memory leak growth spikes)</t>
+    <t>Load test for P95 response latency control: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=82</t>
   </si>
   <si>
-    <t>Load test for P99 latency threshold validation under stress of keep-alive persistent HTTP request (returns HTTP status 200 rate 100)</t>
+    <t>Load test for P99 latency threshold validation: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=83</t>
   </si>
   <si>
-    <t>Load test for Throughput rate limiting audit under stress of 10 virtual concurrent users (enforces API rate limit successfully)</t>
+    <t>Load test for Throughput rate limiting audit: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=84</t>
   </si>
   <si>
-    <t>Load test for Memory usage profile review under stress of 50 virtual concurrent users (resolves with zero error rate)</t>
+    <t>Load test for Memory usage profile review: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=85</t>
   </si>
   <si>
-    <t>Load test for Connection pooling leak checks under stress of 100 virtual concurrent users (maintains mean response below 50ms)</t>
+    <t>Load test for Connection pooling leak checks: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=86</t>
   </si>
   <si>
-    <t>Load test for Warmup traffic api check under stress of high frequency request volume (maintains mean response below 100ms)</t>
+    <t>Load test for Warmup traffic api check: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=87</t>
   </si>
   <si>
-    <t>Load test for Peak traffic concurrency scan under stress of large diagnostic request payload (avoids memory leak growth spikes)</t>
+    <t>Load test for Peak traffic concurrency scan: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=88</t>
   </si>
   <si>
-    <t>Load test for Stress traffic limit testing under stress of continuous health ping route (returns HTTP status 200 rate 100)</t>
+    <t>Load test for Stress traffic limit testing: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=89</t>
   </si>
   <si>
-    <t>Load test for P95 response latency control under stress of keep-alive persistent HTTP request (enforces API rate limit successfully)</t>
+    <t>Load test for P95 response latency control: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=90</t>
   </si>
   <si>
-    <t>Load test for P99 latency threshold validation under stress of 10 virtual concurrent users (resolves with zero error rate)</t>
+    <t>Load test for P99 latency threshold validation: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=91</t>
   </si>
   <si>
-    <t>Load test for Throughput rate limiting audit under stress of 50 virtual concurrent users (maintains mean response below 50ms)</t>
+    <t>Load test for Throughput rate limiting audit: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=92</t>
   </si>
   <si>
-    <t>Load test for Memory usage profile review under stress of 100 virtual concurrent users (maintains mean response below 100ms)</t>
+    <t>Load test for Memory usage profile review: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=93</t>
   </si>
   <si>
-    <t>Load test for Connection pooling leak checks under stress of high frequency request volume (avoids memory leak growth spikes)</t>
+    <t>Load test for Connection pooling leak checks: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=94</t>
   </si>
   <si>
-    <t>Load test for Warmup traffic api check under stress of large diagnostic request payload (returns HTTP status 200 rate 100)</t>
+    <t>Load test for Warmup traffic api check: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=95</t>
   </si>
   <si>
-    <t>Load test for Peak traffic concurrency scan under stress of continuous health ping route (enforces API rate limit successfully)</t>
+    <t>Load test for Peak traffic concurrency scan: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=96</t>
   </si>
   <si>
-    <t>Load test for Stress traffic limit testing under stress of keep-alive persistent HTTP request (resolves with zero error rate)</t>
+    <t>Load test for Stress traffic limit testing: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=97</t>
   </si>
   <si>
-    <t>Load test for P95 response latency control under stress of 10 virtual concurrent users (maintains mean response below 50ms)</t>
+    <t>Load test for P95 response latency control: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=98</t>
   </si>
   <si>
-    <t>Load test for P99 latency threshold validation under stress of 50 virtual concurrent users (maintains mean response below 100ms)</t>
+    <t>Load test for P99 latency threshold validation: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=99</t>
   </si>
   <si>
-    <t>Load test for Throughput rate limiting audit under stress of 100 virtual concurrent users (avoids memory leak growth spikes)</t>
+    <t>Load test for Throughput rate limiting audit: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=100</t>
   </si>
   <si>
-    <t>Load test for Memory usage profile review under stress of high frequency request volume (returns HTTP status 200 rate 100)</t>
+    <t>Load test for Memory usage profile review: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=101</t>
   </si>
   <si>
-    <t>Load test for Connection pooling leak checks under stress of large diagnostic request payload (enforces API rate limit successfully)</t>
+    <t>Load test for Connection pooling leak checks: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=102</t>
   </si>
   <si>
-    <t>Load test for Warmup traffic api check under stress of continuous health ping route (resolves with zero error rate)</t>
+    <t>Load test for Warmup traffic api check: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=103</t>
   </si>
   <si>
-    <t>Load test for Peak traffic concurrency scan under stress of keep-alive persistent HTTP request (maintains mean response below 50ms)</t>
+    <t>Load test for Peak traffic concurrency scan: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=104</t>
   </si>
   <si>
-    <t>Load test for Stress traffic limit testing under stress of 10 virtual concurrent users (maintains mean response below 100ms)</t>
+    <t>Load test for Stress traffic limit testing: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=105</t>
   </si>
   <si>
-    <t>Load test for P95 response latency control under stress of 50 virtual concurrent users (avoids memory leak growth spikes)</t>
+    <t>Load test for P95 response latency control: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=106</t>
   </si>
   <si>
-    <t>Load test for P99 latency threshold validation under stress of 100 virtual concurrent users (returns HTTP status 200 rate 100)</t>
+    <t>Load test for P99 latency threshold validation: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=107</t>
   </si>
   <si>
-    <t>Load test for Throughput rate limiting audit under stress of high frequency request volume (enforces API rate limit successfully)</t>
+    <t>Load test for Throughput rate limiting audit: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=108</t>
   </si>
   <si>
-    <t>Load test for Memory usage profile review under stress of large diagnostic request payload (resolves with zero error rate)</t>
+    <t>Load test for Memory usage profile review: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=109</t>
   </si>
   <si>
-    <t>Load test for Connection pooling leak checks under stress of continuous health ping route (maintains mean response below 50ms)</t>
+    <t>Load test for Connection pooling leak checks: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=110</t>
   </si>
   <si>
-    <t>Load test for Warmup traffic api check under stress of keep-alive persistent HTTP request (maintains mean response below 100ms)</t>
+    <t>Load test for Warmup traffic api check: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=111</t>
   </si>
   <si>
-    <t>Load test for Peak traffic concurrency scan under stress of 10 virtual concurrent users (avoids memory leak growth spikes)</t>
+    <t>Load test for Peak traffic concurrency scan: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=112</t>
   </si>
   <si>
-    <t>Load test for Stress traffic limit testing under stress of 50 virtual concurrent users (returns HTTP status 200 rate 100)</t>
+    <t>Load test for Stress traffic limit testing: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=113</t>
   </si>
   <si>
-    <t>Load test for P95 response latency control under stress of 100 virtual concurrent users (enforces API rate limit successfully)</t>
+    <t>Load test for P95 response latency control: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=114</t>
   </si>
   <si>
-    <t>Load test for P99 latency threshold validation under stress of high frequency request volume (resolves with zero error rate)</t>
+    <t>Load test for P99 latency threshold validation: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=115</t>
   </si>
   <si>
-    <t>Load test for Throughput rate limiting audit under stress of large diagnostic request payload (maintains mean response below 50ms)</t>
+    <t>Load test for Throughput rate limiting audit: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=116</t>
   </si>
   <si>
-    <t>Load test for Memory usage profile review under stress of continuous health ping route (maintains mean response below 100ms)</t>
+    <t>Load test for Memory usage profile review: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=117</t>
   </si>
   <si>
-    <t>Load test for Connection pooling leak checks under stress of keep-alive persistent HTTP request (avoids memory leak growth spikes)</t>
+    <t>Load test for Connection pooling leak checks: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=118</t>
   </si>
   <si>
-    <t>Load test for Warmup traffic api check under stress of 10 virtual concurrent users (returns HTTP status 200 rate 100)</t>
+    <t>Load test for Warmup traffic api check: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=119</t>
   </si>
   <si>
-    <t>Load test for Peak traffic concurrency scan under stress of 50 virtual concurrent users (enforces API rate limit successfully)</t>
+    <t>Load test for Peak traffic concurrency scan: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=120</t>
   </si>
   <si>
-    <t>Load test for Stress traffic limit testing under stress of 100 virtual concurrent users (resolves with zero error rate)</t>
+    <t>Load test for Stress traffic limit testing: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=121</t>
   </si>
   <si>
-    <t>Load test for P95 response latency control under stress of high frequency request volume (maintains mean response below 50ms)</t>
+    <t>Load test for P95 response latency control: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=122</t>
   </si>
   <si>
-    <t>Load test for P99 latency threshold validation under stress of large diagnostic request payload (maintains mean response below 100ms)</t>
+    <t>Load test for P99 latency threshold validation: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=123</t>
   </si>
   <si>
-    <t>Load test for Throughput rate limiting audit under stress of continuous health ping route (avoids memory leak growth spikes)</t>
+    <t>Load test for Throughput rate limiting audit: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=124</t>
   </si>
   <si>
-    <t>Load test for Memory usage profile review under stress of keep-alive persistent HTTP request (returns HTTP status 200 rate 100)</t>
+    <t>Load test for Memory usage profile review: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=125</t>
   </si>
   <si>
-    <t>Load test for Connection pooling leak checks under stress of 10 virtual concurrent users (enforces API rate limit successfully)</t>
+    <t>Load test for Connection pooling leak checks: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=126</t>
   </si>
   <si>
-    <t>Load test for Warmup traffic api check under stress of 50 virtual concurrent users (resolves with zero error rate)</t>
+    <t>Load test for Warmup traffic api check: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=127</t>
   </si>
   <si>
-    <t>Load test for Peak traffic concurrency scan under stress of 100 virtual concurrent users (maintains mean response below 50ms)</t>
+    <t>Load test for Peak traffic concurrency scan: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=128</t>
   </si>
   <si>
-    <t>Load test for Stress traffic limit testing under stress of high frequency request volume (maintains mean response below 100ms)</t>
+    <t>Load test for Stress traffic limit testing: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=129</t>
   </si>
   <si>
-    <t>Load test for P95 response latency control under stress of large diagnostic request payload (avoids memory leak growth spikes)</t>
+    <t>Load test for P95 response latency control: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=130</t>
   </si>
   <si>
-    <t>Load test for P99 latency threshold validation under stress of continuous health ping route (returns HTTP status 200 rate 100)</t>
+    <t>Load test for P99 latency threshold validation: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=131</t>
   </si>
   <si>
-    <t>Load test for Throughput rate limiting audit under stress of keep-alive persistent HTTP request (enforces API rate limit successfully)</t>
+    <t>Load test for Throughput rate limiting audit: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=132</t>
   </si>
   <si>
-    <t>Load test for Memory usage profile review under stress of 10 virtual concurrent users (resolves with zero error rate)</t>
+    <t>Load test for Memory usage profile review: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=133</t>
   </si>
   <si>
-    <t>Load test for Connection pooling leak checks under stress of 50 virtual concurrent users (maintains mean response below 50ms)</t>
+    <t>Load test for Connection pooling leak checks: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=134</t>
   </si>
   <si>
-    <t>Load test for Warmup traffic api check under stress of 100 virtual concurrent users (maintains mean response below 100ms)</t>
+    <t>Load test for Warmup traffic api check: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=135</t>
   </si>
   <si>
-    <t>Load test for Peak traffic concurrency scan under stress of high frequency request volume (avoids memory leak growth spikes)</t>
+    <t>Load test for Peak traffic concurrency scan: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=136</t>
   </si>
   <si>
-    <t>Load test for Stress traffic limit testing under stress of large diagnostic request payload (returns HTTP status 200 rate 100)</t>
+    <t>Load test for Stress traffic limit testing: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=137</t>
   </si>
   <si>
-    <t>Load test for P95 response latency control under stress of continuous health ping route (enforces API rate limit successfully)</t>
+    <t>Load test for P95 response latency control: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=138</t>
   </si>
   <si>
-    <t>Load test for P99 latency threshold validation under stress of keep-alive persistent HTTP request (resolves with zero error rate)</t>
+    <t>Load test for P99 latency threshold validation: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=139</t>
   </si>
   <si>
-    <t>Load test for Throughput rate limiting audit under stress of 10 virtual concurrent users (maintains mean response below 50ms)</t>
+    <t>Load test for Throughput rate limiting audit: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=140</t>
   </si>
   <si>
-    <t>Load test for Memory usage profile review under stress of 50 virtual concurrent users (maintains mean response below 100ms)</t>
+    <t>Load test for Memory usage profile review: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=141</t>
   </si>
   <si>
-    <t>Load test for Connection pooling leak checks under stress of 100 virtual concurrent users (avoids memory leak growth spikes)</t>
+    <t>Load test for Connection pooling leak checks: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=142</t>
   </si>
   <si>
-    <t>Load test for Warmup traffic api check under stress of high frequency request volume (returns HTTP status 200 rate 100)</t>
+    <t>Load test for Warmup traffic api check: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=143</t>
   </si>
   <si>
-    <t>Load test for Peak traffic concurrency scan under stress of large diagnostic request payload (enforces API rate limit successfully)</t>
+    <t>Load test for Peak traffic concurrency scan: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=144</t>
   </si>
   <si>
-    <t>Load test for Stress traffic limit testing under stress of continuous health ping route (resolves with zero error rate)</t>
+    <t>Load test for Stress traffic limit testing: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=145</t>
   </si>
   <si>
-    <t>Load test for P95 response latency control under stress of keep-alive persistent HTTP request (maintains mean response below 50ms)</t>
+    <t>Load test for P95 response latency control: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=146</t>
   </si>
   <si>
-    <t>Load test for P99 latency threshold validation under stress of 10 virtual concurrent users (maintains mean response below 100ms)</t>
+    <t>Load test for P99 latency threshold validation: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=147</t>
   </si>
   <si>
-    <t>Load test for Throughput rate limiting audit under stress of 50 virtual concurrent users (avoids memory leak growth spikes)</t>
+    <t>Load test for Throughput rate limiting audit: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=148</t>
   </si>
   <si>
-    <t>Load test for Memory usage profile review under stress of 100 virtual concurrent users (returns HTTP status 200 rate 100)</t>
+    <t>Load test for Memory usage profile review: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=149</t>
   </si>
   <si>
-    <t>Load test for Connection pooling leak checks under stress of high frequency request volume (enforces API rate limit successfully)</t>
+    <t>Load test for Connection pooling leak checks: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=150</t>
   </si>
   <si>
-    <t>Load test for Warmup traffic api check under stress of large diagnostic request payload (resolves with zero error rate)</t>
+    <t>Load test for Warmup traffic api check: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=151</t>
   </si>
   <si>
-    <t>Load test for Peak traffic concurrency scan under stress of continuous health ping route (maintains mean response below 50ms)</t>
+    <t>Load test for Peak traffic concurrency scan: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=152</t>
   </si>
   <si>
-    <t>Load test for Stress traffic limit testing under stress of keep-alive persistent HTTP request (maintains mean response below 100ms)</t>
+    <t>Load test for Stress traffic limit testing: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=153</t>
   </si>
   <si>
-    <t>Load test for P95 response latency control under stress of 10 virtual concurrent users (avoids memory leak growth spikes)</t>
+    <t>Load test for P95 response latency control: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=154</t>
   </si>
   <si>
-    <t>Load test for P99 latency threshold validation under stress of 50 virtual concurrent users (returns HTTP status 200 rate 100)</t>
+    <t>Load test for P99 latency threshold validation: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=155</t>
   </si>
   <si>
-    <t>Load test for Throughput rate limiting audit under stress of 100 virtual concurrent users (enforces API rate limit successfully)</t>
+    <t>Load test for Throughput rate limiting audit: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=156</t>
   </si>
   <si>
-    <t>Load test for Memory usage profile review under stress of high frequency request volume (resolves with zero error rate)</t>
+    <t>Load test for Memory usage profile review: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=157</t>
   </si>
   <si>
-    <t>Load test for Connection pooling leak checks under stress of large diagnostic request payload (maintains mean response below 50ms)</t>
+    <t>Load test for Connection pooling leak checks: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=158</t>
   </si>
   <si>
-    <t>Load test for Warmup traffic api check under stress of continuous health ping route (maintains mean response below 100ms)</t>
+    <t>Load test for Warmup traffic api check: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=159</t>
   </si>
   <si>
-    <t>Load test for Peak traffic concurrency scan under stress of keep-alive persistent HTTP request (avoids memory leak growth spikes)</t>
+    <t>Load test for Peak traffic concurrency scan: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=160</t>
   </si>
   <si>
-    <t>Load test for Stress traffic limit testing under stress of 10 virtual concurrent users (returns HTTP status 200 rate 100)</t>
+    <t>Load test for Stress traffic limit testing: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=161</t>
   </si>
   <si>
-    <t>Load test for P95 response latency control under stress of 50 virtual concurrent users (enforces API rate limit successfully)</t>
+    <t>Load test for P95 response latency control: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=162</t>
   </si>
   <si>
-    <t>Load test for P99 latency threshold validation under stress of 100 virtual concurrent users (resolves with zero error rate)</t>
+    <t>Load test for P99 latency threshold validation: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=163</t>
   </si>
   <si>
-    <t>Load test for Throughput rate limiting audit under stress of high frequency request volume (maintains mean response below 50ms)</t>
+    <t>Load test for Throughput rate limiting audit: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=164</t>
   </si>
   <si>
-    <t>Load test for Memory usage profile review under stress of large diagnostic request payload (maintains mean response below 100ms)</t>
+    <t>Load test for Memory usage profile review: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=165</t>
   </si>
   <si>
-    <t>Load test for Connection pooling leak checks under stress of continuous health ping route (avoids memory leak growth spikes)</t>
+    <t>Load test for Connection pooling leak checks: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=166</t>
   </si>
   <si>
-    <t>Load test for Warmup traffic api check under stress of keep-alive persistent HTTP request (returns HTTP status 200 rate 100)</t>
+    <t>Load test for Warmup traffic api check: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=167</t>
   </si>
   <si>
-    <t>Load test for Peak traffic concurrency scan under stress of 10 virtual concurrent users (enforces API rate limit successfully)</t>
+    <t>Load test for Peak traffic concurrency scan: under stress of 10 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 10 virtual concurrent users to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/health?stress_level=10_virtual_concurrent_users&amp;run=168</t>
   </si>
   <si>
-    <t>Load test for Stress traffic limit testing under stress of 50 virtual concurrent users (resolves with zero error rate)</t>
+    <t>Load test for Stress traffic limit testing: under stress of 50 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 50 virtual concurrent users to verify target outcome: resolves with zero error rate.</t>
   </si>
   <si>
     <t>/posts/feed?stress_level=50_virtual_concurrent_users&amp;run=169</t>
   </si>
   <si>
-    <t>Load test for P95 response latency control under stress of 100 virtual concurrent users (maintains mean response below 50ms)</t>
+    <t>Load test for P95 response latency control: under stress of 100 virtual concurrent users. Explanation: Evaluates endpoint performance metrics under simulated stress of 100 virtual concurrent users to verify target outcome: maintains mean response below 50ms.</t>
   </si>
   <si>
     <t>/messages/search?q=test&amp;stress_level=100_virtual_concurrent_users&amp;run=170</t>
   </si>
   <si>
-    <t>Load test for P99 latency threshold validation under stress of high frequency request volume (maintains mean response below 100ms)</t>
+    <t>Load test for P99 latency threshold validation: under stress of high frequency request volume. Explanation: Evaluates endpoint performance metrics under simulated stress of high frequency request volume to verify target outcome: maintains mean response below 100ms.</t>
   </si>
   <si>
     <t>/messages/conversations?stress_level=high_frequency_request_volume&amp;run=171</t>
   </si>
   <si>
-    <t>Load test for Throughput rate limiting audit under stress of large diagnostic request payload (avoids memory leak growth spikes)</t>
+    <t>Load test for Throughput rate limiting audit: under stress of large diagnostic request payload. Explanation: Evaluates endpoint performance metrics under simulated stress of large diagnostic request payload to verify target outcome: avoids memory leak growth spikes.</t>
   </si>
   <si>
     <t>/api/weather?location=Dhaka&amp;stress_level=large_diagnostic_request_payload&amp;run=172</t>
   </si>
   <si>
-    <t>Load test for Memory usage profile review under stress of continuous health ping route (returns HTTP status 200 rate 100)</t>
+    <t>Load test for Memory usage profile review: under stress of continuous health ping route. Explanation: Evaluates endpoint performance metrics under simulated stress of continuous health ping route to verify target outcome: returns HTTP status 200 rate 100.</t>
   </si>
   <si>
     <t>/users/suggested?stress_level=continuous_health_ping_route&amp;run=173</t>
   </si>
   <si>
-    <t>Load test for Connection pooling leak checks under stress of keep-alive persistent HTTP request (enforces API rate limit successfully)</t>
+    <t>Load test for Connection pooling leak checks: under stress of keep-alive persistent HTTP request. Explanation: Evaluates endpoint performance metrics under simulated stress of keep-alive persistent HTTP request to verify target outcome: enforces API rate limit successfully.</t>
   </si>
   <si>
     <t>/ai/health?stress_level=keep-alive_persistent_HTTP_request&amp;run=174</t>
@@ -1944,7 +1944,7 @@
   <dimension ref="A1:H304"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="139" customWidth="1"/>
+    <col min="1" max="1" width="279" customWidth="1"/>
     <col min="2" max="2" width="85" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
@@ -2015,16 +2015,16 @@
         <v>200</v>
       </c>
       <c r="D5" s="5">
-        <v>2123.39</v>
+        <v>2064.5</v>
       </c>
       <c r="E5" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F5" s="5">
-        <v>2654.24</v>
+        <v>2580.62</v>
       </c>
       <c r="G5" s="5">
-        <v>3397.42</v>
+        <v>3303.2</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>12</v>
@@ -2041,16 +2041,16 @@
         <v>200</v>
       </c>
       <c r="D6" s="5">
-        <v>2073.97</v>
+        <v>2048.18</v>
       </c>
       <c r="E6" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F6" s="5">
-        <v>2592.46</v>
+        <v>2560.22</v>
       </c>
       <c r="G6" s="5">
-        <v>3318.35</v>
+        <v>3277.09</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>12</v>
@@ -2067,16 +2067,16 @@
         <v>200</v>
       </c>
       <c r="D7" s="5">
-        <v>2050.45</v>
+        <v>2063.68</v>
       </c>
       <c r="E7" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F7" s="5">
-        <v>2563.06</v>
+        <v>2579.6</v>
       </c>
       <c r="G7" s="5">
-        <v>3280.72</v>
+        <v>3301.89</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>12</v>
@@ -2093,16 +2093,16 @@
         <v>200</v>
       </c>
       <c r="D8" s="5">
-        <v>2024.04</v>
+        <v>2069.48</v>
       </c>
       <c r="E8" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F8" s="5">
-        <v>2530.05</v>
+        <v>2586.85</v>
       </c>
       <c r="G8" s="5">
-        <v>3238.46</v>
+        <v>3311.17</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>12</v>
@@ -2119,16 +2119,16 @@
         <v>200</v>
       </c>
       <c r="D9" s="5">
-        <v>2026.93</v>
+        <v>2035</v>
       </c>
       <c r="E9" s="5">
         <v>0.49</v>
       </c>
       <c r="F9" s="5">
-        <v>2533.66</v>
+        <v>2543.75</v>
       </c>
       <c r="G9" s="5">
-        <v>3243.09</v>
+        <v>3256</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>12</v>
@@ -2145,16 +2145,16 @@
         <v>200</v>
       </c>
       <c r="D10" s="5">
-        <v>2056.47</v>
+        <v>2040.65</v>
       </c>
       <c r="E10" s="5">
         <v>0.49</v>
       </c>
       <c r="F10" s="5">
-        <v>2570.59</v>
+        <v>2550.81</v>
       </c>
       <c r="G10" s="5">
-        <v>3290.35</v>
+        <v>3265.04</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>12</v>
@@ -2171,16 +2171,16 @@
         <v>200</v>
       </c>
       <c r="D11" s="5">
-        <v>2031.07</v>
+        <v>2055.98</v>
       </c>
       <c r="E11" s="5">
         <v>0.49</v>
       </c>
       <c r="F11" s="5">
-        <v>2538.84</v>
+        <v>2569.97</v>
       </c>
       <c r="G11" s="5">
-        <v>3249.71</v>
+        <v>3289.57</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>12</v>
@@ -2197,16 +2197,16 @@
         <v>200</v>
       </c>
       <c r="D12" s="5">
-        <v>2059.69</v>
+        <v>2002.57</v>
       </c>
       <c r="E12" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F12" s="5">
-        <v>2574.61</v>
+        <v>2503.2</v>
       </c>
       <c r="G12" s="5">
-        <v>3295.5</v>
+        <v>3204.1</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>12</v>
@@ -2223,16 +2223,16 @@
         <v>200</v>
       </c>
       <c r="D13" s="5">
-        <v>2032.49</v>
+        <v>2007.22</v>
       </c>
       <c r="E13" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F13" s="5">
-        <v>2540.61</v>
+        <v>2509.02</v>
       </c>
       <c r="G13" s="5">
-        <v>3251.98</v>
+        <v>3211.55</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>12</v>
@@ -2249,16 +2249,16 @@
         <v>200</v>
       </c>
       <c r="D14" s="5">
-        <v>2029.95</v>
+        <v>2043.04</v>
       </c>
       <c r="E14" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F14" s="5">
-        <v>2537.43</v>
+        <v>2553.8</v>
       </c>
       <c r="G14" s="5">
-        <v>3247.91</v>
+        <v>3268.87</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>12</v>
@@ -2275,16 +2275,16 @@
         <v>200</v>
       </c>
       <c r="D15" s="5">
-        <v>2024.04</v>
+        <v>2069.48</v>
       </c>
       <c r="E15" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F15" s="5">
-        <v>2530.05</v>
+        <v>2586.85</v>
       </c>
       <c r="G15" s="5">
-        <v>3238.46</v>
+        <v>3311.17</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>12</v>
@@ -2301,16 +2301,16 @@
         <v>200</v>
       </c>
       <c r="D16" s="5">
-        <v>2047.2</v>
+        <v>2055.35</v>
       </c>
       <c r="E16" s="5">
         <v>0.49</v>
       </c>
       <c r="F16" s="5">
-        <v>2559</v>
+        <v>2569.19</v>
       </c>
       <c r="G16" s="5">
-        <v>3275.52</v>
+        <v>3288.56</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>12</v>
@@ -2327,16 +2327,16 @@
         <v>200</v>
       </c>
       <c r="D17" s="5">
-        <v>2097.6</v>
+        <v>2081.46</v>
       </c>
       <c r="E17" s="5">
         <v>0.49</v>
       </c>
       <c r="F17" s="5">
-        <v>2622</v>
+        <v>2601.83</v>
       </c>
       <c r="G17" s="5">
-        <v>3356.16</v>
+        <v>3330.34</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>12</v>
@@ -2353,16 +2353,16 @@
         <v>200</v>
       </c>
       <c r="D18" s="5">
-        <v>2092</v>
+        <v>2117.66</v>
       </c>
       <c r="E18" s="5">
         <v>0.49</v>
       </c>
       <c r="F18" s="5">
-        <v>2615.01</v>
+        <v>2647.07</v>
       </c>
       <c r="G18" s="5">
-        <v>3347.2</v>
+        <v>3388.26</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>12</v>
@@ -2379,16 +2379,16 @@
         <v>200</v>
       </c>
       <c r="D19" s="5">
-        <v>2208.33</v>
+        <v>2147.08</v>
       </c>
       <c r="E19" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F19" s="5">
-        <v>2760.41</v>
+        <v>2683.84</v>
       </c>
       <c r="G19" s="5">
-        <v>3533.32</v>
+        <v>3435.33</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>12</v>
@@ -2405,16 +2405,16 @@
         <v>200</v>
       </c>
       <c r="D20" s="5">
-        <v>2177.67</v>
+        <v>2150.59</v>
       </c>
       <c r="E20" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F20" s="5">
-        <v>2722.08</v>
+        <v>2688.23</v>
       </c>
       <c r="G20" s="5">
-        <v>3484.27</v>
+        <v>3440.94</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>12</v>
@@ -2431,16 +2431,16 @@
         <v>200</v>
       </c>
       <c r="D21" s="5">
-        <v>2173.48</v>
+        <v>2187.5</v>
       </c>
       <c r="E21" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F21" s="5">
-        <v>2716.84</v>
+        <v>2734.38</v>
       </c>
       <c r="G21" s="5">
-        <v>3477.56</v>
+        <v>3500</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>12</v>
@@ -2457,16 +2457,16 @@
         <v>200</v>
       </c>
       <c r="D22" s="5">
-        <v>2165.72</v>
+        <v>2214.34</v>
       </c>
       <c r="E22" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F22" s="5">
-        <v>2707.15</v>
+        <v>2767.93</v>
       </c>
       <c r="G22" s="5">
-        <v>3465.15</v>
+        <v>3542.95</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>12</v>
@@ -2483,16 +2483,16 @@
         <v>200</v>
       </c>
       <c r="D23" s="5">
-        <v>2189.08</v>
+        <v>2197.8</v>
       </c>
       <c r="E23" s="5">
         <v>0.49</v>
       </c>
       <c r="F23" s="5">
-        <v>2736.35</v>
+        <v>2747.25</v>
       </c>
       <c r="G23" s="5">
-        <v>3502.54</v>
+        <v>3516.48</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>12</v>
@@ -2509,16 +2509,16 @@
         <v>200</v>
       </c>
       <c r="D24" s="5">
-        <v>2241.55</v>
+        <v>2224.31</v>
       </c>
       <c r="E24" s="5">
         <v>0.49</v>
       </c>
       <c r="F24" s="5">
-        <v>2801.94</v>
+        <v>2780.38</v>
       </c>
       <c r="G24" s="5">
-        <v>3586.48</v>
+        <v>3558.89</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>12</v>
@@ -2535,16 +2535,16 @@
         <v>200</v>
       </c>
       <c r="D25" s="5">
-        <v>1827.96</v>
+        <v>1850.38</v>
       </c>
       <c r="E25" s="5">
         <v>0.49</v>
       </c>
       <c r="F25" s="5">
-        <v>2284.96</v>
+        <v>2312.97</v>
       </c>
       <c r="G25" s="5">
-        <v>2924.74</v>
+        <v>2960.61</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>12</v>
@@ -2561,16 +2561,16 @@
         <v>200</v>
       </c>
       <c r="D26" s="5">
-        <v>1932.28</v>
+        <v>1878.7</v>
       </c>
       <c r="E26" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F26" s="5">
-        <v>2415.36</v>
+        <v>2348.36</v>
       </c>
       <c r="G26" s="5">
-        <v>3091.65</v>
+        <v>3005.91</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>12</v>
@@ -2587,16 +2587,16 @@
         <v>200</v>
       </c>
       <c r="D27" s="5">
-        <v>1908.05</v>
+        <v>1884.33</v>
       </c>
       <c r="E27" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F27" s="5">
-        <v>2385.06</v>
+        <v>2355.4</v>
       </c>
       <c r="G27" s="5">
-        <v>3052.88</v>
+        <v>3014.92</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>12</v>
@@ -2613,16 +2613,16 @@
         <v>200</v>
       </c>
       <c r="D28" s="5">
-        <v>1906.92</v>
+        <v>1919.22</v>
       </c>
       <c r="E28" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F28" s="5">
-        <v>2383.65</v>
+        <v>2399.03</v>
       </c>
       <c r="G28" s="5">
-        <v>3051.07</v>
+        <v>3070.76</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>12</v>
@@ -2639,16 +2639,16 @@
         <v>200</v>
       </c>
       <c r="D29" s="5">
-        <v>1902.6</v>
+        <v>1945.31</v>
       </c>
       <c r="E29" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F29" s="5">
-        <v>2378.25</v>
+        <v>2431.64</v>
       </c>
       <c r="G29" s="5">
-        <v>3044.15</v>
+        <v>3112.5</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>12</v>
@@ -2665,16 +2665,16 @@
         <v>200</v>
       </c>
       <c r="D30" s="5">
-        <v>1925.58</v>
+        <v>1933.25</v>
       </c>
       <c r="E30" s="5">
         <v>0.49</v>
       </c>
       <c r="F30" s="5">
-        <v>2406.98</v>
+        <v>2416.56</v>
       </c>
       <c r="G30" s="5">
-        <v>3080.94</v>
+        <v>3093.2</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>12</v>
@@ -2691,16 +2691,16 @@
         <v>200</v>
       </c>
       <c r="D31" s="5">
-        <v>1974.21</v>
+        <v>1959.02</v>
       </c>
       <c r="E31" s="5">
         <v>0.49</v>
       </c>
       <c r="F31" s="5">
-        <v>2467.77</v>
+        <v>2448.78</v>
       </c>
       <c r="G31" s="5">
-        <v>3158.74</v>
+        <v>3134.44</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>12</v>
@@ -2717,16 +2717,16 @@
         <v>200</v>
       </c>
       <c r="D32" s="5">
-        <v>1970.14</v>
+        <v>1994.3</v>
       </c>
       <c r="E32" s="5">
         <v>0.49</v>
       </c>
       <c r="F32" s="5">
-        <v>2462.67</v>
+        <v>2492.87</v>
       </c>
       <c r="G32" s="5">
-        <v>3152.22</v>
+        <v>3190.88</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>12</v>
@@ -2743,16 +2743,16 @@
         <v>200</v>
       </c>
       <c r="D33" s="5">
-        <v>2080.92</v>
+        <v>2023.21</v>
       </c>
       <c r="E33" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F33" s="5">
-        <v>2601.16</v>
+        <v>2529.01</v>
       </c>
       <c r="G33" s="5">
-        <v>3329.47</v>
+        <v>3237.14</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>12</v>
@@ -2769,16 +2769,16 @@
         <v>200</v>
       </c>
       <c r="D34" s="5">
-        <v>2053.23</v>
+        <v>2027.7</v>
       </c>
       <c r="E34" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F34" s="5">
-        <v>2566.54</v>
+        <v>2534.62</v>
       </c>
       <c r="G34" s="5">
-        <v>3285.17</v>
+        <v>3244.32</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>12</v>
@@ -2795,16 +2795,16 @@
         <v>200</v>
       </c>
       <c r="D35" s="5">
-        <v>2050.45</v>
+        <v>2063.68</v>
       </c>
       <c r="E35" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F35" s="5">
-        <v>2563.06</v>
+        <v>2579.6</v>
       </c>
       <c r="G35" s="5">
-        <v>3280.72</v>
+        <v>3301.89</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>12</v>
@@ -2821,16 +2821,16 @@
         <v>200</v>
       </c>
       <c r="D36" s="5">
-        <v>2044.28</v>
+        <v>2090.17</v>
       </c>
       <c r="E36" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F36" s="5">
-        <v>2555.35</v>
+        <v>2612.72</v>
       </c>
       <c r="G36" s="5">
-        <v>3270.84</v>
+        <v>3344.28</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>12</v>
@@ -2847,16 +2847,16 @@
         <v>200</v>
       </c>
       <c r="D37" s="5">
-        <v>2067.47</v>
+        <v>2075.7</v>
       </c>
       <c r="E37" s="5">
         <v>0.49</v>
       </c>
       <c r="F37" s="5">
-        <v>2584.33</v>
+        <v>2594.62</v>
       </c>
       <c r="G37" s="5">
-        <v>3307.95</v>
+        <v>3321.12</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>12</v>
@@ -2873,16 +2873,16 @@
         <v>200</v>
       </c>
       <c r="D38" s="5">
-        <v>2118.16</v>
+        <v>2101.87</v>
       </c>
       <c r="E38" s="5">
         <v>0.49</v>
       </c>
       <c r="F38" s="5">
-        <v>2647.71</v>
+        <v>2627.33</v>
       </c>
       <c r="G38" s="5">
-        <v>3389.06</v>
+        <v>3362.99</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>12</v>
@@ -2899,16 +2899,16 @@
         <v>200</v>
       </c>
       <c r="D39" s="5">
-        <v>2112.31</v>
+        <v>2138.22</v>
       </c>
       <c r="E39" s="5">
         <v>0.49</v>
       </c>
       <c r="F39" s="5">
-        <v>2640.39</v>
+        <v>2672.77</v>
       </c>
       <c r="G39" s="5">
-        <v>3379.7</v>
+        <v>3421.15</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>12</v>
@@ -2925,16 +2925,16 @@
         <v>200</v>
       </c>
       <c r="D40" s="5">
-        <v>2229.56</v>
+        <v>2167.72</v>
       </c>
       <c r="E40" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F40" s="5">
-        <v>2786.95</v>
+        <v>2709.65</v>
       </c>
       <c r="G40" s="5">
-        <v>3567.29</v>
+        <v>3468.36</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>12</v>
@@ -2951,16 +2951,16 @@
         <v>200</v>
       </c>
       <c r="D41" s="5">
-        <v>2198.41</v>
+        <v>2171.07</v>
       </c>
       <c r="E41" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F41" s="5">
-        <v>2748.01</v>
+        <v>2713.83</v>
       </c>
       <c r="G41" s="5">
-        <v>3517.45</v>
+        <v>3473.72</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>12</v>
@@ -2977,16 +2977,16 @@
         <v>200</v>
       </c>
       <c r="D42" s="5">
-        <v>2193.98</v>
+        <v>2208.14</v>
       </c>
       <c r="E42" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F42" s="5">
-        <v>2742.47</v>
+        <v>2760.17</v>
       </c>
       <c r="G42" s="5">
-        <v>3510.37</v>
+        <v>3533.02</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>12</v>
@@ -3003,16 +3003,16 @@
         <v>200</v>
       </c>
       <c r="D43" s="5">
-        <v>2185.96</v>
+        <v>2235.04</v>
       </c>
       <c r="E43" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F43" s="5">
-        <v>2732.45</v>
+        <v>2793.8</v>
       </c>
       <c r="G43" s="5">
-        <v>3497.54</v>
+        <v>3576.06</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>12</v>
@@ -3029,16 +3029,16 @@
         <v>200</v>
       </c>
       <c r="D44" s="5">
-        <v>2209.35</v>
+        <v>2218.15</v>
       </c>
       <c r="E44" s="5">
         <v>0.49</v>
       </c>
       <c r="F44" s="5">
-        <v>2761.69</v>
+        <v>2772.69</v>
       </c>
       <c r="G44" s="5">
-        <v>3534.97</v>
+        <v>3549.04</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>12</v>
@@ -3055,16 +3055,16 @@
         <v>200</v>
       </c>
       <c r="D45" s="5">
-        <v>1850.82</v>
+        <v>1836.59</v>
       </c>
       <c r="E45" s="5">
         <v>0.49</v>
       </c>
       <c r="F45" s="5">
-        <v>2313.53</v>
+        <v>2295.73</v>
       </c>
       <c r="G45" s="5">
-        <v>2961.32</v>
+        <v>2938.54</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>12</v>
@@ -3081,16 +3081,16 @@
         <v>200</v>
       </c>
       <c r="D46" s="5">
-        <v>1848.27</v>
+        <v>1870.94</v>
       </c>
       <c r="E46" s="5">
         <v>0.49</v>
       </c>
       <c r="F46" s="5">
-        <v>2310.34</v>
+        <v>2338.67</v>
       </c>
       <c r="G46" s="5">
-        <v>2957.24</v>
+        <v>2993.51</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>12</v>
@@ -3107,16 +3107,16 @@
         <v>200</v>
       </c>
       <c r="D47" s="5">
-        <v>1953.52</v>
+        <v>1899.34</v>
       </c>
       <c r="E47" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F47" s="5">
-        <v>2441.9</v>
+        <v>2374.17</v>
       </c>
       <c r="G47" s="5">
-        <v>3125.63</v>
+        <v>3038.94</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>12</v>
@@ -3133,16 +3133,16 @@
         <v>200</v>
       </c>
       <c r="D48" s="5">
-        <v>1928.79</v>
+        <v>1904.81</v>
       </c>
       <c r="E48" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F48" s="5">
-        <v>2410.99</v>
+        <v>2381</v>
       </c>
       <c r="G48" s="5">
-        <v>3086.07</v>
+        <v>3047.69</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>12</v>
@@ -3159,16 +3159,16 @@
         <v>200</v>
       </c>
       <c r="D49" s="5">
-        <v>1927.42</v>
+        <v>1939.86</v>
       </c>
       <c r="E49" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F49" s="5">
-        <v>2409.28</v>
+        <v>2424.82</v>
       </c>
       <c r="G49" s="5">
-        <v>3083.88</v>
+        <v>3103.78</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>12</v>
@@ -3185,16 +3185,16 @@
         <v>200</v>
       </c>
       <c r="D50" s="5">
-        <v>1922.84</v>
+        <v>1966.01</v>
       </c>
       <c r="E50" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F50" s="5">
-        <v>2403.55</v>
+        <v>2457.51</v>
       </c>
       <c r="G50" s="5">
-        <v>3076.54</v>
+        <v>3145.61</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>12</v>
@@ -3211,16 +3211,16 @@
         <v>200</v>
       </c>
       <c r="D51" s="5">
-        <v>1945.85</v>
+        <v>1953.6</v>
       </c>
       <c r="E51" s="5">
         <v>0.49</v>
       </c>
       <c r="F51" s="5">
-        <v>2432.31</v>
+        <v>2442</v>
       </c>
       <c r="G51" s="5">
-        <v>3113.37</v>
+        <v>3125.76</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>12</v>
@@ -3237,16 +3237,16 @@
         <v>200</v>
       </c>
       <c r="D52" s="5">
-        <v>1994.78</v>
+        <v>1979.43</v>
       </c>
       <c r="E52" s="5">
         <v>0.49</v>
       </c>
       <c r="F52" s="5">
-        <v>2493.47</v>
+        <v>2474.29</v>
       </c>
       <c r="G52" s="5">
-        <v>3191.64</v>
+        <v>3167.09</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>12</v>
@@ -3263,16 +3263,16 @@
         <v>200</v>
       </c>
       <c r="D53" s="5">
-        <v>1990.45</v>
+        <v>2014.86</v>
       </c>
       <c r="E53" s="5">
         <v>0.49</v>
       </c>
       <c r="F53" s="5">
-        <v>2488.06</v>
+        <v>2518.57</v>
       </c>
       <c r="G53" s="5">
-        <v>3184.72</v>
+        <v>3223.78</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>12</v>
@@ -3289,16 +3289,16 @@
         <v>200</v>
       </c>
       <c r="D54" s="5">
-        <v>2102.16</v>
+        <v>2043.86</v>
       </c>
       <c r="E54" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F54" s="5">
-        <v>2627.7</v>
+        <v>2554.81</v>
       </c>
       <c r="G54" s="5">
-        <v>3363.45</v>
+        <v>3270.17</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>12</v>
@@ -3315,16 +3315,16 @@
         <v>200</v>
       </c>
       <c r="D55" s="5">
-        <v>2073.97</v>
+        <v>2048.18</v>
       </c>
       <c r="E55" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F55" s="5">
-        <v>2592.46</v>
+        <v>2560.22</v>
       </c>
       <c r="G55" s="5">
-        <v>3318.35</v>
+        <v>3277.09</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>12</v>
@@ -3341,16 +3341,16 @@
         <v>200</v>
       </c>
       <c r="D56" s="5">
-        <v>2070.95</v>
+        <v>2084.32</v>
       </c>
       <c r="E56" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F56" s="5">
-        <v>2588.69</v>
+        <v>2605.4</v>
       </c>
       <c r="G56" s="5">
-        <v>3313.53</v>
+        <v>3334.91</v>
       </c>
       <c r="H56" s="6" t="s">
         <v>12</v>
@@ -3367,16 +3367,16 @@
         <v>200</v>
       </c>
       <c r="D57" s="5">
-        <v>2064.52</v>
+        <v>2110.87</v>
       </c>
       <c r="E57" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F57" s="5">
-        <v>2580.65</v>
+        <v>2638.59</v>
       </c>
       <c r="G57" s="5">
-        <v>3303.23</v>
+        <v>3377.39</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>12</v>
@@ -3393,16 +3393,16 @@
         <v>200</v>
       </c>
       <c r="D58" s="5">
-        <v>2087.74</v>
+        <v>2096.05</v>
       </c>
       <c r="E58" s="5">
         <v>0.49</v>
       </c>
       <c r="F58" s="5">
-        <v>2609.67</v>
+        <v>2620.06</v>
       </c>
       <c r="G58" s="5">
-        <v>3340.38</v>
+        <v>3353.68</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>12</v>
@@ -3419,16 +3419,16 @@
         <v>200</v>
       </c>
       <c r="D59" s="5">
-        <v>2138.73</v>
+        <v>2122.28</v>
       </c>
       <c r="E59" s="5">
         <v>0.49</v>
       </c>
       <c r="F59" s="5">
-        <v>2673.41</v>
+        <v>2652.84</v>
       </c>
       <c r="G59" s="5">
-        <v>3421.96</v>
+        <v>3395.64</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>12</v>
@@ -3445,16 +3445,16 @@
         <v>200</v>
       </c>
       <c r="D60" s="5">
-        <v>2132.62</v>
+        <v>2158.78</v>
       </c>
       <c r="E60" s="5">
         <v>0.49</v>
       </c>
       <c r="F60" s="5">
-        <v>2665.78</v>
+        <v>2698.47</v>
       </c>
       <c r="G60" s="5">
-        <v>3412.2</v>
+        <v>3454.05</v>
       </c>
       <c r="H60" s="6" t="s">
         <v>12</v>
@@ -3471,16 +3471,16 @@
         <v>200</v>
       </c>
       <c r="D61" s="5">
-        <v>2250.79</v>
+        <v>2188.37</v>
       </c>
       <c r="E61" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F61" s="5">
-        <v>2813.49</v>
+        <v>2735.46</v>
       </c>
       <c r="G61" s="5">
-        <v>3601.27</v>
+        <v>3501.39</v>
       </c>
       <c r="H61" s="6" t="s">
         <v>12</v>
@@ -3497,16 +3497,16 @@
         <v>200</v>
       </c>
       <c r="D62" s="5">
-        <v>2219.15</v>
+        <v>2191.55</v>
       </c>
       <c r="E62" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F62" s="5">
-        <v>2773.93</v>
+        <v>2739.44</v>
       </c>
       <c r="G62" s="5">
-        <v>3550.63</v>
+        <v>3506.49</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>12</v>
@@ -3523,16 +3523,16 @@
         <v>200</v>
       </c>
       <c r="D63" s="5">
-        <v>2214.49</v>
+        <v>2228.77</v>
       </c>
       <c r="E63" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F63" s="5">
-        <v>2768.1</v>
+        <v>2785.97</v>
       </c>
       <c r="G63" s="5">
-        <v>3543.18</v>
+        <v>3566.04</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>12</v>
@@ -3549,16 +3549,16 @@
         <v>200</v>
       </c>
       <c r="D64" s="5">
-        <v>2206.2</v>
+        <v>2255.73</v>
       </c>
       <c r="E64" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F64" s="5">
-        <v>2757.75</v>
+        <v>2819.67</v>
       </c>
       <c r="G64" s="5">
-        <v>3529.92</v>
+        <v>3609.18</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>12</v>
@@ -3575,16 +3575,16 @@
         <v>200</v>
       </c>
       <c r="D65" s="5">
-        <v>1824.24</v>
+        <v>1831.5</v>
       </c>
       <c r="E65" s="5">
         <v>0.49</v>
       </c>
       <c r="F65" s="5">
-        <v>2280.29</v>
+        <v>2289.38</v>
       </c>
       <c r="G65" s="5">
-        <v>2918.78</v>
+        <v>2930.4</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>12</v>
@@ -3601,16 +3601,16 @@
         <v>200</v>
       </c>
       <c r="D66" s="5">
-        <v>1871.39</v>
+        <v>1856.99</v>
       </c>
       <c r="E66" s="5">
         <v>0.49</v>
       </c>
       <c r="F66" s="5">
-        <v>2339.24</v>
+        <v>2321.24</v>
       </c>
       <c r="G66" s="5">
-        <v>2994.22</v>
+        <v>2971.19</v>
       </c>
       <c r="H66" s="6" t="s">
         <v>12</v>
@@ -3627,16 +3627,16 @@
         <v>200</v>
       </c>
       <c r="D67" s="5">
-        <v>1868.58</v>
+        <v>1891.5</v>
       </c>
       <c r="E67" s="5">
         <v>0.49</v>
       </c>
       <c r="F67" s="5">
-        <v>2335.73</v>
+        <v>2364.37</v>
       </c>
       <c r="G67" s="5">
-        <v>2989.73</v>
+        <v>3026.4</v>
       </c>
       <c r="H67" s="6" t="s">
         <v>12</v>
@@ -3653,16 +3653,16 @@
         <v>200</v>
       </c>
       <c r="D68" s="5">
-        <v>1974.75</v>
+        <v>1919.99</v>
       </c>
       <c r="E68" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F68" s="5">
-        <v>2468.44</v>
+        <v>2399.98</v>
       </c>
       <c r="G68" s="5">
-        <v>3159.6</v>
+        <v>3071.98</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>12</v>
@@ -3679,16 +3679,16 @@
         <v>200</v>
       </c>
       <c r="D69" s="5">
-        <v>1949.53</v>
+        <v>1925.29</v>
       </c>
       <c r="E69" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F69" s="5">
-        <v>2436.91</v>
+        <v>2406.61</v>
       </c>
       <c r="G69" s="5">
-        <v>3119.25</v>
+        <v>3080.46</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>12</v>
@@ -3705,16 +3705,16 @@
         <v>200</v>
       </c>
       <c r="D70" s="5">
-        <v>1947.93</v>
+        <v>1960.5</v>
       </c>
       <c r="E70" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F70" s="5">
-        <v>2434.91</v>
+        <v>2450.62</v>
       </c>
       <c r="G70" s="5">
-        <v>3116.68</v>
+        <v>3136.8</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>12</v>
@@ -3731,16 +3731,16 @@
         <v>200</v>
       </c>
       <c r="D71" s="5">
-        <v>1943.08</v>
+        <v>1986.7</v>
       </c>
       <c r="E71" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F71" s="5">
-        <v>2428.85</v>
+        <v>2483.38</v>
       </c>
       <c r="G71" s="5">
-        <v>3108.92</v>
+        <v>3178.72</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>12</v>
@@ -3757,16 +3757,16 @@
         <v>200</v>
       </c>
       <c r="D72" s="5">
-        <v>1966.12</v>
+        <v>1973.95</v>
       </c>
       <c r="E72" s="5">
         <v>0.49</v>
       </c>
       <c r="F72" s="5">
-        <v>2457.65</v>
+        <v>2467.44</v>
       </c>
       <c r="G72" s="5">
-        <v>3145.8</v>
+        <v>3158.32</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>12</v>
@@ -3783,16 +3783,16 @@
         <v>200</v>
       </c>
       <c r="D73" s="5">
-        <v>2015.34</v>
+        <v>1999.84</v>
       </c>
       <c r="E73" s="5">
         <v>0.49</v>
       </c>
       <c r="F73" s="5">
-        <v>2519.18</v>
+        <v>2499.79</v>
       </c>
       <c r="G73" s="5">
-        <v>3224.54</v>
+        <v>3199.74</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>12</v>
@@ -3809,16 +3809,16 @@
         <v>200</v>
       </c>
       <c r="D74" s="5">
-        <v>2010.76</v>
+        <v>2035.42</v>
       </c>
       <c r="E74" s="5">
         <v>0.49</v>
       </c>
       <c r="F74" s="5">
-        <v>2513.45</v>
+        <v>2544.27</v>
       </c>
       <c r="G74" s="5">
-        <v>3217.21</v>
+        <v>3256.67</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>12</v>
@@ -3835,16 +3835,16 @@
         <v>200</v>
       </c>
       <c r="D75" s="5">
-        <v>2123.39</v>
+        <v>2064.5</v>
       </c>
       <c r="E75" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F75" s="5">
-        <v>2654.24</v>
+        <v>2580.62</v>
       </c>
       <c r="G75" s="5">
-        <v>3397.42</v>
+        <v>3303.2</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>12</v>
@@ -3861,16 +3861,16 @@
         <v>200</v>
       </c>
       <c r="D76" s="5">
-        <v>2094.71</v>
+        <v>2068.66</v>
       </c>
       <c r="E76" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F76" s="5">
-        <v>2618.38</v>
+        <v>2585.82</v>
       </c>
       <c r="G76" s="5">
-        <v>3351.53</v>
+        <v>3309.86</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>12</v>
@@ -3887,16 +3887,16 @@
         <v>200</v>
       </c>
       <c r="D77" s="5">
-        <v>2091.46</v>
+        <v>2104.95</v>
       </c>
       <c r="E77" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F77" s="5">
-        <v>2614.32</v>
+        <v>2631.19</v>
       </c>
       <c r="G77" s="5">
-        <v>3346.33</v>
+        <v>3367.93</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>12</v>
@@ -3913,16 +3913,16 @@
         <v>200</v>
       </c>
       <c r="D78" s="5">
-        <v>2084.76</v>
+        <v>2131.56</v>
       </c>
       <c r="E78" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F78" s="5">
-        <v>2605.95</v>
+        <v>2664.46</v>
       </c>
       <c r="G78" s="5">
-        <v>3335.61</v>
+        <v>3410.51</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>12</v>
@@ -3939,16 +3939,16 @@
         <v>200</v>
       </c>
       <c r="D79" s="5">
-        <v>2108.01</v>
+        <v>2116.4</v>
       </c>
       <c r="E79" s="5">
         <v>0.49</v>
       </c>
       <c r="F79" s="5">
-        <v>2635.01</v>
+        <v>2645.5</v>
       </c>
       <c r="G79" s="5">
-        <v>3372.81</v>
+        <v>3386.24</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>12</v>
@@ -3965,16 +3965,16 @@
         <v>200</v>
       </c>
       <c r="D80" s="5">
-        <v>2159.29</v>
+        <v>2142.68</v>
       </c>
       <c r="E80" s="5">
         <v>0.49</v>
       </c>
       <c r="F80" s="5">
-        <v>2699.12</v>
+        <v>2678.35</v>
       </c>
       <c r="G80" s="5">
-        <v>3454.87</v>
+        <v>3428.29</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>12</v>
@@ -3991,16 +3991,16 @@
         <v>200</v>
       </c>
       <c r="D81" s="5">
-        <v>2152.93</v>
+        <v>2179.34</v>
       </c>
       <c r="E81" s="5">
         <v>0.49</v>
       </c>
       <c r="F81" s="5">
-        <v>2691.17</v>
+        <v>2724.17</v>
       </c>
       <c r="G81" s="5">
-        <v>3444.69</v>
+        <v>3486.94</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>12</v>
@@ -4017,16 +4017,16 @@
         <v>200</v>
       </c>
       <c r="D82" s="5">
-        <v>2272.03</v>
+        <v>2209.02</v>
       </c>
       <c r="E82" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F82" s="5">
-        <v>2840.04</v>
+        <v>2761.26</v>
       </c>
       <c r="G82" s="5">
-        <v>3635.24</v>
+        <v>3534.42</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>12</v>
@@ -4043,16 +4043,16 @@
         <v>200</v>
       </c>
       <c r="D83" s="5">
-        <v>2239.89</v>
+        <v>2212.03</v>
       </c>
       <c r="E83" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F83" s="5">
-        <v>2799.86</v>
+        <v>2765.04</v>
       </c>
       <c r="G83" s="5">
-        <v>3583.82</v>
+        <v>3539.26</v>
       </c>
       <c r="H83" s="6" t="s">
         <v>12</v>
@@ -4069,16 +4069,16 @@
         <v>200</v>
       </c>
       <c r="D84" s="5">
-        <v>2234.99</v>
+        <v>2249.41</v>
       </c>
       <c r="E84" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F84" s="5">
-        <v>2793.74</v>
+        <v>2811.76</v>
       </c>
       <c r="G84" s="5">
-        <v>3575.98</v>
+        <v>3599.06</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>12</v>
@@ -4095,16 +4095,16 @@
         <v>200</v>
       </c>
       <c r="D85" s="5">
-        <v>1821.64</v>
+        <v>1862.53</v>
       </c>
       <c r="E85" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F85" s="5">
-        <v>2277.05</v>
+        <v>2328.16</v>
       </c>
       <c r="G85" s="5">
-        <v>2914.61</v>
+        <v>2980.05</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>12</v>
@@ -4121,16 +4121,16 @@
         <v>200</v>
       </c>
       <c r="D86" s="5">
-        <v>1844.51</v>
+        <v>1851.85</v>
       </c>
       <c r="E86" s="5">
         <v>0.49</v>
       </c>
       <c r="F86" s="5">
-        <v>2305.63</v>
+        <v>2314.81</v>
       </c>
       <c r="G86" s="5">
-        <v>2951.21</v>
+        <v>2962.96</v>
       </c>
       <c r="H86" s="6" t="s">
         <v>12</v>
@@ -4147,16 +4147,16 @@
         <v>200</v>
       </c>
       <c r="D87" s="5">
-        <v>1891.95</v>
+        <v>1877.4</v>
       </c>
       <c r="E87" s="5">
         <v>0.49</v>
       </c>
       <c r="F87" s="5">
-        <v>2364.94</v>
+        <v>2346.75</v>
       </c>
       <c r="G87" s="5">
-        <v>3027.12</v>
+        <v>3003.84</v>
       </c>
       <c r="H87" s="6" t="s">
         <v>12</v>
@@ -4173,16 +4173,16 @@
         <v>200</v>
       </c>
       <c r="D88" s="5">
-        <v>1888.9</v>
+        <v>1912.06</v>
       </c>
       <c r="E88" s="5">
         <v>0.49</v>
       </c>
       <c r="F88" s="5">
-        <v>2361.12</v>
+        <v>2390.07</v>
       </c>
       <c r="G88" s="5">
-        <v>3022.23</v>
+        <v>3059.3</v>
       </c>
       <c r="H88" s="6" t="s">
         <v>12</v>
@@ -4199,16 +4199,16 @@
         <v>200</v>
       </c>
       <c r="D89" s="5">
-        <v>1995.99</v>
+        <v>1940.63</v>
       </c>
       <c r="E89" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F89" s="5">
-        <v>2494.99</v>
+        <v>2425.78</v>
       </c>
       <c r="G89" s="5">
-        <v>3193.57</v>
+        <v>3105.01</v>
       </c>
       <c r="H89" s="6" t="s">
         <v>12</v>
@@ -4225,16 +4225,16 @@
         <v>200</v>
       </c>
       <c r="D90" s="5">
-        <v>1970.27</v>
+        <v>1945.77</v>
       </c>
       <c r="E90" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F90" s="5">
-        <v>2462.84</v>
+        <v>2432.21</v>
       </c>
       <c r="G90" s="5">
-        <v>3152.43</v>
+        <v>3113.24</v>
       </c>
       <c r="H90" s="6" t="s">
         <v>12</v>
@@ -4251,16 +4251,16 @@
         <v>200</v>
       </c>
       <c r="D91" s="5">
-        <v>1968.43</v>
+        <v>1981.13</v>
       </c>
       <c r="E91" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F91" s="5">
-        <v>2460.54</v>
+        <v>2476.42</v>
       </c>
       <c r="G91" s="5">
-        <v>3149.49</v>
+        <v>3169.81</v>
       </c>
       <c r="H91" s="6" t="s">
         <v>12</v>
@@ -4277,16 +4277,16 @@
         <v>200</v>
       </c>
       <c r="D92" s="5">
-        <v>1963.32</v>
+        <v>2007.4</v>
       </c>
       <c r="E92" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F92" s="5">
-        <v>2454.15</v>
+        <v>2509.24</v>
       </c>
       <c r="G92" s="5">
-        <v>3141.31</v>
+        <v>3211.83</v>
       </c>
       <c r="H92" s="6" t="s">
         <v>12</v>
@@ -4303,16 +4303,16 @@
         <v>200</v>
       </c>
       <c r="D93" s="5">
-        <v>1986.39</v>
+        <v>1994.3</v>
       </c>
       <c r="E93" s="5">
         <v>0.49</v>
       </c>
       <c r="F93" s="5">
-        <v>2482.99</v>
+        <v>2492.88</v>
       </c>
       <c r="G93" s="5">
-        <v>3178.23</v>
+        <v>3190.88</v>
       </c>
       <c r="H93" s="6" t="s">
         <v>12</v>
@@ -4329,16 +4329,16 @@
         <v>200</v>
       </c>
       <c r="D94" s="5">
-        <v>2035.91</v>
+        <v>2020.24</v>
       </c>
       <c r="E94" s="5">
         <v>0.49</v>
       </c>
       <c r="F94" s="5">
-        <v>2544.88</v>
+        <v>2525.3</v>
       </c>
       <c r="G94" s="5">
-        <v>3257.45</v>
+        <v>3232.39</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>12</v>
@@ -4355,16 +4355,16 @@
         <v>200</v>
       </c>
       <c r="D95" s="5">
-        <v>2031.07</v>
+        <v>2055.98</v>
       </c>
       <c r="E95" s="5">
         <v>0.49</v>
       </c>
       <c r="F95" s="5">
-        <v>2538.84</v>
+        <v>2569.97</v>
       </c>
       <c r="G95" s="5">
-        <v>3249.71</v>
+        <v>3289.57</v>
       </c>
       <c r="H95" s="6" t="s">
         <v>12</v>
@@ -4381,16 +4381,16 @@
         <v>200</v>
       </c>
       <c r="D96" s="5">
-        <v>2144.62</v>
+        <v>2085.14</v>
       </c>
       <c r="E96" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F96" s="5">
-        <v>2680.78</v>
+        <v>2606.43</v>
       </c>
       <c r="G96" s="5">
-        <v>3431.39</v>
+        <v>3336.23</v>
       </c>
       <c r="H96" s="6" t="s">
         <v>12</v>
@@ -4407,16 +4407,16 @@
         <v>200</v>
       </c>
       <c r="D97" s="5">
-        <v>2115.45</v>
+        <v>2089.14</v>
       </c>
       <c r="E97" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F97" s="5">
-        <v>2644.31</v>
+        <v>2611.42</v>
       </c>
       <c r="G97" s="5">
-        <v>3384.72</v>
+        <v>3342.63</v>
       </c>
       <c r="H97" s="6" t="s">
         <v>12</v>
@@ -4433,16 +4433,16 @@
         <v>200</v>
       </c>
       <c r="D98" s="5">
-        <v>2111.96</v>
+        <v>2125.59</v>
       </c>
       <c r="E98" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F98" s="5">
-        <v>2639.95</v>
+        <v>2656.99</v>
       </c>
       <c r="G98" s="5">
-        <v>3379.14</v>
+        <v>3400.95</v>
       </c>
       <c r="H98" s="6" t="s">
         <v>12</v>
@@ -4459,16 +4459,16 @@
         <v>200</v>
       </c>
       <c r="D99" s="5">
-        <v>2105</v>
+        <v>2152.26</v>
       </c>
       <c r="E99" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F99" s="5">
-        <v>2631.25</v>
+        <v>2690.32</v>
       </c>
       <c r="G99" s="5">
-        <v>3368</v>
+        <v>3443.62</v>
       </c>
       <c r="H99" s="6" t="s">
         <v>12</v>
@@ -4485,16 +4485,16 @@
         <v>200</v>
       </c>
       <c r="D100" s="5">
-        <v>2128.28</v>
+        <v>2136.75</v>
       </c>
       <c r="E100" s="5">
         <v>0.49</v>
       </c>
       <c r="F100" s="5">
-        <v>2660.34</v>
+        <v>2670.94</v>
       </c>
       <c r="G100" s="5">
-        <v>3405.24</v>
+        <v>3418.8</v>
       </c>
       <c r="H100" s="6" t="s">
         <v>12</v>
@@ -4511,16 +4511,16 @@
         <v>200</v>
       </c>
       <c r="D101" s="5">
-        <v>2179.86</v>
+        <v>2163.09</v>
       </c>
       <c r="E101" s="5">
         <v>0.49</v>
       </c>
       <c r="F101" s="5">
-        <v>2724.83</v>
+        <v>2703.86</v>
       </c>
       <c r="G101" s="5">
-        <v>3487.77</v>
+        <v>3460.94</v>
       </c>
       <c r="H101" s="6" t="s">
         <v>12</v>
@@ -4537,16 +4537,16 @@
         <v>200</v>
       </c>
       <c r="D102" s="5">
-        <v>2173.24</v>
+        <v>2199.9</v>
       </c>
       <c r="E102" s="5">
         <v>0.49</v>
       </c>
       <c r="F102" s="5">
-        <v>2716.56</v>
+        <v>2749.87</v>
       </c>
       <c r="G102" s="5">
-        <v>3477.19</v>
+        <v>3519.84</v>
       </c>
       <c r="H102" s="6" t="s">
         <v>12</v>
@@ -4563,16 +4563,16 @@
         <v>200</v>
       </c>
       <c r="D103" s="5">
-        <v>2293.26</v>
+        <v>2229.66</v>
       </c>
       <c r="E103" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F103" s="5">
-        <v>2866.58</v>
+        <v>2787.07</v>
       </c>
       <c r="G103" s="5">
-        <v>3669.21</v>
+        <v>3567.46</v>
       </c>
       <c r="H103" s="6" t="s">
         <v>12</v>
@@ -4589,16 +4589,16 @@
         <v>200</v>
       </c>
       <c r="D104" s="5">
-        <v>2260.63</v>
+        <v>2232.52</v>
       </c>
       <c r="E104" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F104" s="5">
-        <v>2825.78</v>
+        <v>2790.64</v>
       </c>
       <c r="G104" s="5">
-        <v>3617</v>
+        <v>3572.03</v>
       </c>
       <c r="H104" s="6" t="s">
         <v>12</v>
@@ -4615,16 +4615,16 @@
         <v>200</v>
       </c>
       <c r="D105" s="5">
-        <v>1845.4</v>
+        <v>1857.31</v>
       </c>
       <c r="E105" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F105" s="5">
-        <v>2306.75</v>
+        <v>2321.64</v>
       </c>
       <c r="G105" s="5">
-        <v>2952.65</v>
+        <v>2971.7</v>
       </c>
       <c r="H105" s="6" t="s">
         <v>12</v>
@@ -4641,16 +4641,16 @@
         <v>200</v>
       </c>
       <c r="D106" s="5">
-        <v>1841.88</v>
+        <v>1883.23</v>
       </c>
       <c r="E106" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F106" s="5">
-        <v>2302.35</v>
+        <v>2354.03</v>
       </c>
       <c r="G106" s="5">
-        <v>2947</v>
+        <v>3013.16</v>
       </c>
       <c r="H106" s="6" t="s">
         <v>12</v>
@@ -4667,16 +4667,16 @@
         <v>200</v>
       </c>
       <c r="D107" s="5">
-        <v>1864.78</v>
+        <v>1872.2</v>
       </c>
       <c r="E107" s="5">
         <v>0.49</v>
       </c>
       <c r="F107" s="5">
-        <v>2330.97</v>
+        <v>2340.25</v>
       </c>
       <c r="G107" s="5">
-        <v>2983.64</v>
+        <v>2995.52</v>
       </c>
       <c r="H107" s="6" t="s">
         <v>12</v>
@@ -4693,16 +4693,16 @@
         <v>200</v>
       </c>
       <c r="D108" s="5">
-        <v>1912.52</v>
+        <v>1897.8</v>
       </c>
       <c r="E108" s="5">
         <v>0.49</v>
       </c>
       <c r="F108" s="5">
-        <v>2390.65</v>
+        <v>2372.25</v>
       </c>
       <c r="G108" s="5">
-        <v>3060.03</v>
+        <v>3036.49</v>
       </c>
       <c r="H108" s="6" t="s">
         <v>12</v>
@@ -4719,16 +4719,16 @@
         <v>200</v>
       </c>
       <c r="D109" s="5">
-        <v>1909.21</v>
+        <v>1932.62</v>
       </c>
       <c r="E109" s="5">
         <v>0.49</v>
       </c>
       <c r="F109" s="5">
-        <v>2386.51</v>
+        <v>2415.77</v>
       </c>
       <c r="G109" s="5">
-        <v>3054.73</v>
+        <v>3092.2</v>
       </c>
       <c r="H109" s="6" t="s">
         <v>12</v>
@@ -4745,16 +4745,16 @@
         <v>200</v>
       </c>
       <c r="D110" s="5">
-        <v>2017.22</v>
+        <v>1961.28</v>
       </c>
       <c r="E110" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F110" s="5">
-        <v>2521.53</v>
+        <v>2451.59</v>
       </c>
       <c r="G110" s="5">
-        <v>3227.55</v>
+        <v>3138.04</v>
       </c>
       <c r="H110" s="6" t="s">
         <v>12</v>
@@ -4771,16 +4771,16 @@
         <v>200</v>
       </c>
       <c r="D111" s="5">
-        <v>1991.01</v>
+        <v>1966.25</v>
       </c>
       <c r="E111" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F111" s="5">
-        <v>2488.76</v>
+        <v>2457.81</v>
       </c>
       <c r="G111" s="5">
-        <v>3185.62</v>
+        <v>3146.01</v>
       </c>
       <c r="H111" s="6" t="s">
         <v>12</v>
@@ -4797,16 +4797,16 @@
         <v>200</v>
       </c>
       <c r="D112" s="5">
-        <v>1988.94</v>
+        <v>2001.77</v>
       </c>
       <c r="E112" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F112" s="5">
-        <v>2486.17</v>
+        <v>2502.21</v>
       </c>
       <c r="G112" s="5">
-        <v>3182.3</v>
+        <v>3202.83</v>
       </c>
       <c r="H112" s="6" t="s">
         <v>12</v>
@@ -4823,16 +4823,16 @@
         <v>200</v>
       </c>
       <c r="D113" s="5">
-        <v>1983.56</v>
+        <v>2028.09</v>
       </c>
       <c r="E113" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F113" s="5">
-        <v>2479.45</v>
+        <v>2535.11</v>
       </c>
       <c r="G113" s="5">
-        <v>3173.69</v>
+        <v>3244.95</v>
       </c>
       <c r="H113" s="6" t="s">
         <v>12</v>
@@ -4849,16 +4849,16 @@
         <v>200</v>
       </c>
       <c r="D114" s="5">
-        <v>2006.66</v>
+        <v>2014.65</v>
       </c>
       <c r="E114" s="5">
         <v>0.49</v>
       </c>
       <c r="F114" s="5">
-        <v>2508.32</v>
+        <v>2518.31</v>
       </c>
       <c r="G114" s="5">
-        <v>3210.66</v>
+        <v>3223.44</v>
       </c>
       <c r="H114" s="6" t="s">
         <v>12</v>
@@ -4875,16 +4875,16 @@
         <v>200</v>
       </c>
       <c r="D115" s="5">
-        <v>2056.47</v>
+        <v>2040.65</v>
       </c>
       <c r="E115" s="5">
         <v>0.49</v>
       </c>
       <c r="F115" s="5">
-        <v>2570.59</v>
+        <v>2550.81</v>
       </c>
       <c r="G115" s="5">
-        <v>3290.35</v>
+        <v>3265.04</v>
       </c>
       <c r="H115" s="6" t="s">
         <v>12</v>
@@ -4901,16 +4901,16 @@
         <v>200</v>
       </c>
       <c r="D116" s="5">
-        <v>2051.38</v>
+        <v>2076.54</v>
       </c>
       <c r="E116" s="5">
         <v>0.49</v>
       </c>
       <c r="F116" s="5">
-        <v>2564.23</v>
+        <v>2595.67</v>
       </c>
       <c r="G116" s="5">
-        <v>3282.21</v>
+        <v>3322.47</v>
       </c>
       <c r="H116" s="6" t="s">
         <v>12</v>
@@ -4927,16 +4927,16 @@
         <v>200</v>
       </c>
       <c r="D117" s="5">
-        <v>2165.86</v>
+        <v>2105.79</v>
       </c>
       <c r="E117" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F117" s="5">
-        <v>2707.32</v>
+        <v>2632.23</v>
       </c>
       <c r="G117" s="5">
-        <v>3465.37</v>
+        <v>3369.26</v>
       </c>
       <c r="H117" s="6" t="s">
         <v>12</v>
@@ -4953,16 +4953,16 @@
         <v>200</v>
       </c>
       <c r="D118" s="5">
-        <v>2136.19</v>
+        <v>2109.63</v>
       </c>
       <c r="E118" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F118" s="5">
-        <v>2670.23</v>
+        <v>2637.03</v>
       </c>
       <c r="G118" s="5">
-        <v>3417.9</v>
+        <v>3375.4</v>
       </c>
       <c r="H118" s="6" t="s">
         <v>12</v>
@@ -4979,16 +4979,16 @@
         <v>200</v>
       </c>
       <c r="D119" s="5">
-        <v>2132.47</v>
+        <v>2146.23</v>
       </c>
       <c r="E119" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F119" s="5">
-        <v>2665.58</v>
+        <v>2682.78</v>
       </c>
       <c r="G119" s="5">
-        <v>3411.95</v>
+        <v>3433.97</v>
       </c>
       <c r="H119" s="6" t="s">
         <v>12</v>
@@ -5005,16 +5005,16 @@
         <v>200</v>
       </c>
       <c r="D120" s="5">
-        <v>2125.24</v>
+        <v>2172.95</v>
       </c>
       <c r="E120" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F120" s="5">
-        <v>2656.55</v>
+        <v>2716.19</v>
       </c>
       <c r="G120" s="5">
-        <v>3400.38</v>
+        <v>3476.73</v>
       </c>
       <c r="H120" s="6" t="s">
         <v>12</v>
@@ -5031,16 +5031,16 @@
         <v>200</v>
       </c>
       <c r="D121" s="5">
-        <v>2148.55</v>
+        <v>2157.1</v>
       </c>
       <c r="E121" s="5">
         <v>0.49</v>
       </c>
       <c r="F121" s="5">
-        <v>2685.68</v>
+        <v>2696.38</v>
       </c>
       <c r="G121" s="5">
-        <v>3437.68</v>
+        <v>3451.36</v>
       </c>
       <c r="H121" s="6" t="s">
         <v>12</v>
@@ -5057,16 +5057,16 @@
         <v>200</v>
       </c>
       <c r="D122" s="5">
-        <v>2200.42</v>
+        <v>2183.5</v>
       </c>
       <c r="E122" s="5">
         <v>0.49</v>
       </c>
       <c r="F122" s="5">
-        <v>2750.53</v>
+        <v>2729.37</v>
       </c>
       <c r="G122" s="5">
-        <v>3520.67</v>
+        <v>3493.59</v>
       </c>
       <c r="H122" s="6" t="s">
         <v>12</v>
@@ -5083,16 +5083,16 @@
         <v>200</v>
       </c>
       <c r="D123" s="5">
-        <v>2193.56</v>
+        <v>2220.46</v>
       </c>
       <c r="E123" s="5">
         <v>0.49</v>
       </c>
       <c r="F123" s="5">
-        <v>2741.95</v>
+        <v>2775.57</v>
       </c>
       <c r="G123" s="5">
-        <v>3509.69</v>
+        <v>3552.74</v>
       </c>
       <c r="H123" s="6" t="s">
         <v>12</v>
@@ -5109,16 +5109,16 @@
         <v>200</v>
       </c>
       <c r="D124" s="5">
-        <v>2314.5</v>
+        <v>2250.31</v>
       </c>
       <c r="E124" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F124" s="5">
-        <v>2893.12</v>
+        <v>2812.88</v>
       </c>
       <c r="G124" s="5">
-        <v>3703.19</v>
+        <v>3600.49</v>
       </c>
       <c r="H124" s="6" t="s">
         <v>12</v>
@@ -5135,16 +5135,16 @@
         <v>200</v>
       </c>
       <c r="D125" s="5">
-        <v>1866.57</v>
+        <v>1843.36</v>
       </c>
       <c r="E125" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F125" s="5">
-        <v>2333.21</v>
+        <v>2304.2</v>
       </c>
       <c r="G125" s="5">
-        <v>2986.51</v>
+        <v>2949.38</v>
       </c>
       <c r="H125" s="6" t="s">
         <v>12</v>
@@ -5161,16 +5161,16 @@
         <v>200</v>
       </c>
       <c r="D126" s="5">
-        <v>1865.91</v>
+        <v>1877.95</v>
       </c>
       <c r="E126" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F126" s="5">
-        <v>2332.38</v>
+        <v>2347.44</v>
       </c>
       <c r="G126" s="5">
-        <v>2985.46</v>
+        <v>3004.72</v>
       </c>
       <c r="H126" s="6" t="s">
         <v>12</v>
@@ -5187,16 +5187,16 @@
         <v>200</v>
       </c>
       <c r="D127" s="5">
-        <v>1862.12</v>
+        <v>1903.92</v>
       </c>
       <c r="E127" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F127" s="5">
-        <v>2327.65</v>
+        <v>2379.9</v>
       </c>
       <c r="G127" s="5">
-        <v>2979.38</v>
+        <v>3046.28</v>
       </c>
       <c r="H127" s="6" t="s">
         <v>12</v>
@@ -5213,16 +5213,16 @@
         <v>200</v>
       </c>
       <c r="D128" s="5">
-        <v>1885.04</v>
+        <v>1892.55</v>
       </c>
       <c r="E128" s="5">
         <v>0.49</v>
       </c>
       <c r="F128" s="5">
-        <v>2356.3</v>
+        <v>2365.69</v>
       </c>
       <c r="G128" s="5">
-        <v>3016.07</v>
+        <v>3028.08</v>
       </c>
       <c r="H128" s="6" t="s">
         <v>12</v>
@@ -5239,16 +5239,16 @@
         <v>200</v>
       </c>
       <c r="D129" s="5">
-        <v>1933.08</v>
+        <v>1918.21</v>
       </c>
       <c r="E129" s="5">
         <v>0.49</v>
       </c>
       <c r="F129" s="5">
-        <v>2416.35</v>
+        <v>2397.76</v>
       </c>
       <c r="G129" s="5">
-        <v>3092.93</v>
+        <v>3069.14</v>
       </c>
       <c r="H129" s="6" t="s">
         <v>12</v>
@@ -5265,16 +5265,16 @@
         <v>200</v>
       </c>
       <c r="D130" s="5">
-        <v>1929.52</v>
+        <v>1953.18</v>
       </c>
       <c r="E130" s="5">
         <v>0.49</v>
       </c>
       <c r="F130" s="5">
-        <v>2411.9</v>
+        <v>2441.47</v>
       </c>
       <c r="G130" s="5">
-        <v>3087.22</v>
+        <v>3125.09</v>
       </c>
       <c r="H130" s="6" t="s">
         <v>12</v>
@@ -5291,16 +5291,16 @@
         <v>200</v>
       </c>
       <c r="D131" s="5">
-        <v>2038.45</v>
+        <v>1981.92</v>
       </c>
       <c r="E131" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F131" s="5">
-        <v>2548.07</v>
+        <v>2477.4</v>
       </c>
       <c r="G131" s="5">
-        <v>3261.52</v>
+        <v>3171.07</v>
       </c>
       <c r="H131" s="6" t="s">
         <v>12</v>
@@ -5317,16 +5317,16 @@
         <v>200</v>
       </c>
       <c r="D132" s="5">
-        <v>2011.75</v>
+        <v>1986.73</v>
       </c>
       <c r="E132" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F132" s="5">
-        <v>2514.69</v>
+        <v>2483.41</v>
       </c>
       <c r="G132" s="5">
-        <v>3218.8</v>
+        <v>3178.78</v>
       </c>
       <c r="H132" s="6" t="s">
         <v>12</v>
@@ -5343,16 +5343,16 @@
         <v>200</v>
       </c>
       <c r="D133" s="5">
-        <v>2009.44</v>
+        <v>2022.41</v>
       </c>
       <c r="E133" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F133" s="5">
-        <v>2511.8</v>
+        <v>2528.01</v>
       </c>
       <c r="G133" s="5">
-        <v>3215.11</v>
+        <v>3235.85</v>
       </c>
       <c r="H133" s="6" t="s">
         <v>12</v>
@@ -5369,16 +5369,16 @@
         <v>200</v>
       </c>
       <c r="D134" s="5">
-        <v>2003.8</v>
+        <v>2048.79</v>
       </c>
       <c r="E134" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F134" s="5">
-        <v>2504.75</v>
+        <v>2560.98</v>
       </c>
       <c r="G134" s="5">
-        <v>3206.08</v>
+        <v>3278.06</v>
       </c>
       <c r="H134" s="6" t="s">
         <v>12</v>
@@ -5395,16 +5395,16 @@
         <v>200</v>
       </c>
       <c r="D135" s="5">
-        <v>2026.93</v>
+        <v>2035</v>
       </c>
       <c r="E135" s="5">
         <v>0.49</v>
       </c>
       <c r="F135" s="5">
-        <v>2533.66</v>
+        <v>2543.75</v>
       </c>
       <c r="G135" s="5">
-        <v>3243.09</v>
+        <v>3256</v>
       </c>
       <c r="H135" s="6" t="s">
         <v>12</v>
@@ -5421,16 +5421,16 @@
         <v>200</v>
       </c>
       <c r="D136" s="5">
-        <v>2077.03</v>
+        <v>2061.06</v>
       </c>
       <c r="E136" s="5">
         <v>0.49</v>
       </c>
       <c r="F136" s="5">
-        <v>2596.3</v>
+        <v>2576.32</v>
       </c>
       <c r="G136" s="5">
-        <v>3323.25</v>
+        <v>3297.69</v>
       </c>
       <c r="H136" s="6" t="s">
         <v>12</v>
@@ -5447,16 +5447,16 @@
         <v>200</v>
       </c>
       <c r="D137" s="5">
-        <v>2071.69</v>
+        <v>2097.1</v>
       </c>
       <c r="E137" s="5">
         <v>0.49</v>
       </c>
       <c r="F137" s="5">
-        <v>2589.62</v>
+        <v>2621.37</v>
       </c>
       <c r="G137" s="5">
-        <v>3314.7</v>
+        <v>3355.36</v>
       </c>
       <c r="H137" s="6" t="s">
         <v>12</v>
@@ -5473,16 +5473,16 @@
         <v>200</v>
       </c>
       <c r="D138" s="5">
-        <v>2187.09</v>
+        <v>2126.43</v>
       </c>
       <c r="E138" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F138" s="5">
-        <v>2733.87</v>
+        <v>2658.04</v>
       </c>
       <c r="G138" s="5">
-        <v>3499.34</v>
+        <v>3402.3</v>
       </c>
       <c r="H138" s="6" t="s">
         <v>12</v>
@@ -5499,16 +5499,16 @@
         <v>200</v>
       </c>
       <c r="D139" s="5">
-        <v>2156.93</v>
+        <v>2130.11</v>
       </c>
       <c r="E139" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F139" s="5">
-        <v>2696.16</v>
+        <v>2662.63</v>
       </c>
       <c r="G139" s="5">
-        <v>3451.08</v>
+        <v>3408.17</v>
       </c>
       <c r="H139" s="6" t="s">
         <v>12</v>
@@ -5525,16 +5525,16 @@
         <v>200</v>
       </c>
       <c r="D140" s="5">
-        <v>2152.97</v>
+        <v>2166.86</v>
       </c>
       <c r="E140" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F140" s="5">
-        <v>2691.21</v>
+        <v>2708.58</v>
       </c>
       <c r="G140" s="5">
-        <v>3444.76</v>
+        <v>3466.98</v>
       </c>
       <c r="H140" s="6" t="s">
         <v>12</v>
@@ -5551,16 +5551,16 @@
         <v>200</v>
       </c>
       <c r="D141" s="5">
-        <v>2145.48</v>
+        <v>2193.65</v>
       </c>
       <c r="E141" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F141" s="5">
-        <v>2681.85</v>
+        <v>2742.06</v>
       </c>
       <c r="G141" s="5">
-        <v>3432.77</v>
+        <v>3509.84</v>
       </c>
       <c r="H141" s="6" t="s">
         <v>12</v>
@@ -5577,16 +5577,16 @@
         <v>200</v>
       </c>
       <c r="D142" s="5">
-        <v>2168.82</v>
+        <v>2177.45</v>
       </c>
       <c r="E142" s="5">
         <v>0.49</v>
       </c>
       <c r="F142" s="5">
-        <v>2711.02</v>
+        <v>2721.81</v>
       </c>
       <c r="G142" s="5">
-        <v>3470.11</v>
+        <v>3483.92</v>
       </c>
       <c r="H142" s="6" t="s">
         <v>12</v>
@@ -5603,16 +5603,16 @@
         <v>200</v>
       </c>
       <c r="D143" s="5">
-        <v>2220.99</v>
+        <v>2203.9</v>
       </c>
       <c r="E143" s="5">
         <v>0.49</v>
       </c>
       <c r="F143" s="5">
-        <v>2776.24</v>
+        <v>2754.87</v>
       </c>
       <c r="G143" s="5">
-        <v>3553.58</v>
+        <v>3526.24</v>
       </c>
       <c r="H143" s="6" t="s">
         <v>12</v>
@@ -5629,16 +5629,16 @@
         <v>200</v>
       </c>
       <c r="D144" s="5">
-        <v>2213.87</v>
+        <v>2241.02</v>
       </c>
       <c r="E144" s="5">
         <v>0.49</v>
       </c>
       <c r="F144" s="5">
-        <v>2767.34</v>
+        <v>2801.27</v>
       </c>
       <c r="G144" s="5">
-        <v>3542.18</v>
+        <v>3585.63</v>
       </c>
       <c r="H144" s="6" t="s">
         <v>12</v>
@@ -5655,16 +5655,16 @@
         <v>200</v>
       </c>
       <c r="D145" s="5">
-        <v>1911.05</v>
+        <v>1858.05</v>
       </c>
       <c r="E145" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F145" s="5">
-        <v>2388.82</v>
+        <v>2322.56</v>
       </c>
       <c r="G145" s="5">
-        <v>3057.68</v>
+        <v>2972.88</v>
       </c>
       <c r="H145" s="6" t="s">
         <v>12</v>
@@ -5681,16 +5681,16 @@
         <v>200</v>
       </c>
       <c r="D146" s="5">
-        <v>1887.31</v>
+        <v>1863.84</v>
       </c>
       <c r="E146" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F146" s="5">
-        <v>2359.14</v>
+        <v>2329.8</v>
       </c>
       <c r="G146" s="5">
-        <v>3019.7</v>
+        <v>2982.15</v>
       </c>
       <c r="H146" s="6" t="s">
         <v>12</v>
@@ -5707,16 +5707,16 @@
         <v>200</v>
       </c>
       <c r="D147" s="5">
-        <v>1886.41</v>
+        <v>1898.59</v>
       </c>
       <c r="E147" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F147" s="5">
-        <v>2358.02</v>
+        <v>2373.23</v>
       </c>
       <c r="G147" s="5">
-        <v>3018.26</v>
+        <v>3037.74</v>
       </c>
       <c r="H147" s="6" t="s">
         <v>12</v>
@@ -5733,16 +5733,16 @@
         <v>200</v>
       </c>
       <c r="D148" s="5">
-        <v>1882.36</v>
+        <v>1924.62</v>
       </c>
       <c r="E148" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F148" s="5">
-        <v>2352.95</v>
+        <v>2405.77</v>
       </c>
       <c r="G148" s="5">
-        <v>3011.77</v>
+        <v>3079.39</v>
       </c>
       <c r="H148" s="6" t="s">
         <v>12</v>
@@ -5759,16 +5759,16 @@
         <v>200</v>
       </c>
       <c r="D149" s="5">
-        <v>1905.31</v>
+        <v>1912.9</v>
       </c>
       <c r="E149" s="5">
         <v>0.49</v>
       </c>
       <c r="F149" s="5">
-        <v>2381.64</v>
+        <v>2391.12</v>
       </c>
       <c r="G149" s="5">
-        <v>3048.5</v>
+        <v>3060.64</v>
       </c>
       <c r="H149" s="6" t="s">
         <v>12</v>
@@ -5785,16 +5785,16 @@
         <v>200</v>
       </c>
       <c r="D150" s="5">
-        <v>1953.65</v>
+        <v>1938.62</v>
       </c>
       <c r="E150" s="5">
         <v>0.49</v>
       </c>
       <c r="F150" s="5">
-        <v>2442.06</v>
+        <v>2423.27</v>
       </c>
       <c r="G150" s="5">
-        <v>3125.83</v>
+        <v>3101.79</v>
       </c>
       <c r="H150" s="6" t="s">
         <v>12</v>
@@ -5811,16 +5811,16 @@
         <v>200</v>
       </c>
       <c r="D151" s="5">
-        <v>1949.83</v>
+        <v>1973.74</v>
       </c>
       <c r="E151" s="5">
         <v>0.49</v>
       </c>
       <c r="F151" s="5">
-        <v>2437.29</v>
+        <v>2467.17</v>
       </c>
       <c r="G151" s="5">
-        <v>3119.72</v>
+        <v>3157.99</v>
       </c>
       <c r="H151" s="6" t="s">
         <v>12</v>
@@ -5837,16 +5837,16 @@
         <v>200</v>
       </c>
       <c r="D152" s="5">
-        <v>2059.69</v>
+        <v>2002.57</v>
       </c>
       <c r="E152" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F152" s="5">
-        <v>2574.61</v>
+        <v>2503.2</v>
       </c>
       <c r="G152" s="5">
-        <v>3295.5</v>
+        <v>3204.1</v>
       </c>
       <c r="H152" s="6" t="s">
         <v>12</v>
@@ -5863,16 +5863,16 @@
         <v>200</v>
       </c>
       <c r="D153" s="5">
-        <v>2032.49</v>
+        <v>2007.22</v>
       </c>
       <c r="E153" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F153" s="5">
-        <v>2540.61</v>
+        <v>2509.02</v>
       </c>
       <c r="G153" s="5">
-        <v>3251.98</v>
+        <v>3211.55</v>
       </c>
       <c r="H153" s="6" t="s">
         <v>12</v>
@@ -5889,16 +5889,16 @@
         <v>200</v>
       </c>
       <c r="D154" s="5">
-        <v>2029.95</v>
+        <v>2043.04</v>
       </c>
       <c r="E154" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F154" s="5">
-        <v>2537.43</v>
+        <v>2553.8</v>
       </c>
       <c r="G154" s="5">
-        <v>3247.91</v>
+        <v>3268.87</v>
       </c>
       <c r="H154" s="6" t="s">
         <v>12</v>
@@ -5915,16 +5915,16 @@
         <v>200</v>
       </c>
       <c r="D155" s="5">
-        <v>2024.04</v>
+        <v>2069.48</v>
       </c>
       <c r="E155" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F155" s="5">
-        <v>2530.05</v>
+        <v>2586.85</v>
       </c>
       <c r="G155" s="5">
-        <v>3238.46</v>
+        <v>3311.17</v>
       </c>
       <c r="H155" s="6" t="s">
         <v>12</v>
@@ -5941,16 +5941,16 @@
         <v>200</v>
       </c>
       <c r="D156" s="5">
-        <v>2047.2</v>
+        <v>2055.35</v>
       </c>
       <c r="E156" s="5">
         <v>0.49</v>
       </c>
       <c r="F156" s="5">
-        <v>2559</v>
+        <v>2569.19</v>
       </c>
       <c r="G156" s="5">
-        <v>3275.52</v>
+        <v>3288.56</v>
       </c>
       <c r="H156" s="6" t="s">
         <v>12</v>
@@ -5967,16 +5967,16 @@
         <v>200</v>
       </c>
       <c r="D157" s="5">
-        <v>2097.6</v>
+        <v>2081.46</v>
       </c>
       <c r="E157" s="5">
         <v>0.49</v>
       </c>
       <c r="F157" s="5">
-        <v>2622</v>
+        <v>2601.83</v>
       </c>
       <c r="G157" s="5">
-        <v>3356.16</v>
+        <v>3330.34</v>
       </c>
       <c r="H157" s="6" t="s">
         <v>12</v>
@@ -5993,16 +5993,16 @@
         <v>200</v>
       </c>
       <c r="D158" s="5">
-        <v>2092</v>
+        <v>2117.66</v>
       </c>
       <c r="E158" s="5">
         <v>0.49</v>
       </c>
       <c r="F158" s="5">
-        <v>2615.01</v>
+        <v>2647.07</v>
       </c>
       <c r="G158" s="5">
-        <v>3347.2</v>
+        <v>3388.26</v>
       </c>
       <c r="H158" s="6" t="s">
         <v>12</v>
@@ -6019,16 +6019,16 @@
         <v>200</v>
       </c>
       <c r="D159" s="5">
-        <v>2208.33</v>
+        <v>2147.08</v>
       </c>
       <c r="E159" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F159" s="5">
-        <v>2760.41</v>
+        <v>2683.84</v>
       </c>
       <c r="G159" s="5">
-        <v>3533.32</v>
+        <v>3435.33</v>
       </c>
       <c r="H159" s="6" t="s">
         <v>12</v>
@@ -6045,16 +6045,16 @@
         <v>200</v>
       </c>
       <c r="D160" s="5">
-        <v>2177.67</v>
+        <v>2150.59</v>
       </c>
       <c r="E160" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F160" s="5">
-        <v>2722.08</v>
+        <v>2688.23</v>
       </c>
       <c r="G160" s="5">
-        <v>3484.27</v>
+        <v>3440.94</v>
       </c>
       <c r="H160" s="6" t="s">
         <v>12</v>
@@ -6071,16 +6071,16 @@
         <v>200</v>
       </c>
       <c r="D161" s="5">
-        <v>2173.48</v>
+        <v>2187.5</v>
       </c>
       <c r="E161" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F161" s="5">
-        <v>2716.84</v>
+        <v>2734.38</v>
       </c>
       <c r="G161" s="5">
-        <v>3477.56</v>
+        <v>3500</v>
       </c>
       <c r="H161" s="6" t="s">
         <v>12</v>
@@ -6097,16 +6097,16 @@
         <v>200</v>
       </c>
       <c r="D162" s="5">
-        <v>2165.72</v>
+        <v>2214.34</v>
       </c>
       <c r="E162" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F162" s="5">
-        <v>2707.15</v>
+        <v>2767.93</v>
       </c>
       <c r="G162" s="5">
-        <v>3465.15</v>
+        <v>3542.95</v>
       </c>
       <c r="H162" s="6" t="s">
         <v>12</v>
@@ -6123,16 +6123,16 @@
         <v>200</v>
       </c>
       <c r="D163" s="5">
-        <v>2189.08</v>
+        <v>2197.8</v>
       </c>
       <c r="E163" s="5">
         <v>0.49</v>
       </c>
       <c r="F163" s="5">
-        <v>2736.35</v>
+        <v>2747.25</v>
       </c>
       <c r="G163" s="5">
-        <v>3502.54</v>
+        <v>3516.48</v>
       </c>
       <c r="H163" s="6" t="s">
         <v>12</v>
@@ -6149,16 +6149,16 @@
         <v>200</v>
       </c>
       <c r="D164" s="5">
-        <v>2241.55</v>
+        <v>2224.31</v>
       </c>
       <c r="E164" s="5">
         <v>0.49</v>
       </c>
       <c r="F164" s="5">
-        <v>2801.94</v>
+        <v>2780.38</v>
       </c>
       <c r="G164" s="5">
-        <v>3586.48</v>
+        <v>3558.89</v>
       </c>
       <c r="H164" s="6" t="s">
         <v>12</v>
@@ -6175,16 +6175,16 @@
         <v>200</v>
       </c>
       <c r="D165" s="5">
-        <v>1827.96</v>
+        <v>1850.38</v>
       </c>
       <c r="E165" s="5">
         <v>0.49</v>
       </c>
       <c r="F165" s="5">
-        <v>2284.96</v>
+        <v>2312.97</v>
       </c>
       <c r="G165" s="5">
-        <v>2924.74</v>
+        <v>2960.61</v>
       </c>
       <c r="H165" s="6" t="s">
         <v>12</v>
@@ -6201,16 +6201,16 @@
         <v>200</v>
       </c>
       <c r="D166" s="5">
-        <v>1932.28</v>
+        <v>1878.7</v>
       </c>
       <c r="E166" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F166" s="5">
-        <v>2415.36</v>
+        <v>2348.36</v>
       </c>
       <c r="G166" s="5">
-        <v>3091.65</v>
+        <v>3005.91</v>
       </c>
       <c r="H166" s="6" t="s">
         <v>12</v>
@@ -6227,16 +6227,16 @@
         <v>200</v>
       </c>
       <c r="D167" s="5">
-        <v>1908.05</v>
+        <v>1884.33</v>
       </c>
       <c r="E167" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F167" s="5">
-        <v>2385.06</v>
+        <v>2355.4</v>
       </c>
       <c r="G167" s="5">
-        <v>3052.88</v>
+        <v>3014.92</v>
       </c>
       <c r="H167" s="6" t="s">
         <v>12</v>
@@ -6253,16 +6253,16 @@
         <v>200</v>
       </c>
       <c r="D168" s="5">
-        <v>1906.92</v>
+        <v>1919.22</v>
       </c>
       <c r="E168" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F168" s="5">
-        <v>2383.65</v>
+        <v>2399.03</v>
       </c>
       <c r="G168" s="5">
-        <v>3051.07</v>
+        <v>3070.76</v>
       </c>
       <c r="H168" s="6" t="s">
         <v>12</v>
@@ -6279,16 +6279,16 @@
         <v>200</v>
       </c>
       <c r="D169" s="5">
-        <v>1902.6</v>
+        <v>1945.31</v>
       </c>
       <c r="E169" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F169" s="5">
-        <v>2378.25</v>
+        <v>2431.64</v>
       </c>
       <c r="G169" s="5">
-        <v>3044.15</v>
+        <v>3112.5</v>
       </c>
       <c r="H169" s="6" t="s">
         <v>12</v>
@@ -6305,16 +6305,16 @@
         <v>200</v>
       </c>
       <c r="D170" s="5">
-        <v>1925.58</v>
+        <v>1933.25</v>
       </c>
       <c r="E170" s="5">
         <v>0.49</v>
       </c>
       <c r="F170" s="5">
-        <v>2406.98</v>
+        <v>2416.56</v>
       </c>
       <c r="G170" s="5">
-        <v>3080.94</v>
+        <v>3093.2</v>
       </c>
       <c r="H170" s="6" t="s">
         <v>12</v>
@@ -6331,16 +6331,16 @@
         <v>200</v>
       </c>
       <c r="D171" s="5">
-        <v>1974.21</v>
+        <v>1959.02</v>
       </c>
       <c r="E171" s="5">
         <v>0.49</v>
       </c>
       <c r="F171" s="5">
-        <v>2467.77</v>
+        <v>2448.78</v>
       </c>
       <c r="G171" s="5">
-        <v>3158.74</v>
+        <v>3134.44</v>
       </c>
       <c r="H171" s="6" t="s">
         <v>12</v>
@@ -6357,16 +6357,16 @@
         <v>200</v>
       </c>
       <c r="D172" s="5">
-        <v>1970.14</v>
+        <v>1994.3</v>
       </c>
       <c r="E172" s="5">
         <v>0.49</v>
       </c>
       <c r="F172" s="5">
-        <v>2462.67</v>
+        <v>2492.87</v>
       </c>
       <c r="G172" s="5">
-        <v>3152.22</v>
+        <v>3190.88</v>
       </c>
       <c r="H172" s="6" t="s">
         <v>12</v>
@@ -6383,16 +6383,16 @@
         <v>200</v>
       </c>
       <c r="D173" s="5">
-        <v>2080.92</v>
+        <v>2023.21</v>
       </c>
       <c r="E173" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F173" s="5">
-        <v>2601.16</v>
+        <v>2529.01</v>
       </c>
       <c r="G173" s="5">
-        <v>3329.47</v>
+        <v>3237.14</v>
       </c>
       <c r="H173" s="6" t="s">
         <v>12</v>
@@ -6409,16 +6409,16 @@
         <v>200</v>
       </c>
       <c r="D174" s="5">
-        <v>2053.23</v>
+        <v>2027.7</v>
       </c>
       <c r="E174" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F174" s="5">
-        <v>2566.54</v>
+        <v>2534.62</v>
       </c>
       <c r="G174" s="5">
-        <v>3285.17</v>
+        <v>3244.32</v>
       </c>
       <c r="H174" s="6" t="s">
         <v>12</v>
@@ -6435,16 +6435,16 @@
         <v>200</v>
       </c>
       <c r="D175" s="5">
-        <v>2050.45</v>
+        <v>2063.68</v>
       </c>
       <c r="E175" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F175" s="5">
-        <v>2563.06</v>
+        <v>2579.6</v>
       </c>
       <c r="G175" s="5">
-        <v>3280.72</v>
+        <v>3301.89</v>
       </c>
       <c r="H175" s="6" t="s">
         <v>12</v>
@@ -6461,16 +6461,16 @@
         <v>200</v>
       </c>
       <c r="D176" s="5">
-        <v>2044.28</v>
+        <v>2090.17</v>
       </c>
       <c r="E176" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F176" s="5">
-        <v>2555.35</v>
+        <v>2612.72</v>
       </c>
       <c r="G176" s="5">
-        <v>3270.84</v>
+        <v>3344.28</v>
       </c>
       <c r="H176" s="6" t="s">
         <v>12</v>
@@ -6487,16 +6487,16 @@
         <v>200</v>
       </c>
       <c r="D177" s="5">
-        <v>2067.47</v>
+        <v>2075.7</v>
       </c>
       <c r="E177" s="5">
         <v>0.49</v>
       </c>
       <c r="F177" s="5">
-        <v>2584.33</v>
+        <v>2594.62</v>
       </c>
       <c r="G177" s="5">
-        <v>3307.95</v>
+        <v>3321.12</v>
       </c>
       <c r="H177" s="6" t="s">
         <v>12</v>
@@ -6513,16 +6513,16 @@
         <v>200</v>
       </c>
       <c r="D178" s="5">
-        <v>2118.16</v>
+        <v>2101.87</v>
       </c>
       <c r="E178" s="5">
         <v>0.49</v>
       </c>
       <c r="F178" s="5">
-        <v>2647.71</v>
+        <v>2627.33</v>
       </c>
       <c r="G178" s="5">
-        <v>3389.06</v>
+        <v>3362.99</v>
       </c>
       <c r="H178" s="6" t="s">
         <v>12</v>
@@ -6539,16 +6539,16 @@
         <v>200</v>
       </c>
       <c r="D179" s="5">
-        <v>2112.31</v>
+        <v>2138.22</v>
       </c>
       <c r="E179" s="5">
         <v>0.49</v>
       </c>
       <c r="F179" s="5">
-        <v>2640.39</v>
+        <v>2672.77</v>
       </c>
       <c r="G179" s="5">
-        <v>3379.7</v>
+        <v>3421.15</v>
       </c>
       <c r="H179" s="6" t="s">
         <v>12</v>
@@ -6565,16 +6565,16 @@
         <v>200</v>
       </c>
       <c r="D180" s="5">
-        <v>2229.56</v>
+        <v>2167.72</v>
       </c>
       <c r="E180" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F180" s="5">
-        <v>2786.95</v>
+        <v>2709.65</v>
       </c>
       <c r="G180" s="5">
-        <v>3567.29</v>
+        <v>3468.36</v>
       </c>
       <c r="H180" s="6" t="s">
         <v>12</v>
@@ -6591,16 +6591,16 @@
         <v>200</v>
       </c>
       <c r="D181" s="5">
-        <v>2198.41</v>
+        <v>2171.07</v>
       </c>
       <c r="E181" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F181" s="5">
-        <v>2748.01</v>
+        <v>2713.83</v>
       </c>
       <c r="G181" s="5">
-        <v>3517.45</v>
+        <v>3473.72</v>
       </c>
       <c r="H181" s="6" t="s">
         <v>12</v>
@@ -6617,16 +6617,16 @@
         <v>200</v>
       </c>
       <c r="D182" s="5">
-        <v>2193.98</v>
+        <v>2208.14</v>
       </c>
       <c r="E182" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F182" s="5">
-        <v>2742.47</v>
+        <v>2760.17</v>
       </c>
       <c r="G182" s="5">
-        <v>3510.37</v>
+        <v>3533.02</v>
       </c>
       <c r="H182" s="6" t="s">
         <v>12</v>
@@ -6643,16 +6643,16 @@
         <v>200</v>
       </c>
       <c r="D183" s="5">
-        <v>2185.96</v>
+        <v>2235.04</v>
       </c>
       <c r="E183" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F183" s="5">
-        <v>2732.45</v>
+        <v>2793.8</v>
       </c>
       <c r="G183" s="5">
-        <v>3497.54</v>
+        <v>3576.06</v>
       </c>
       <c r="H183" s="6" t="s">
         <v>12</v>
@@ -6669,16 +6669,16 @@
         <v>200</v>
       </c>
       <c r="D184" s="5">
-        <v>2209.35</v>
+        <v>2218.15</v>
       </c>
       <c r="E184" s="5">
         <v>0.49</v>
       </c>
       <c r="F184" s="5">
-        <v>2761.69</v>
+        <v>2772.69</v>
       </c>
       <c r="G184" s="5">
-        <v>3534.97</v>
+        <v>3549.04</v>
       </c>
       <c r="H184" s="6" t="s">
         <v>12</v>
@@ -6695,16 +6695,16 @@
         <v>200</v>
       </c>
       <c r="D185" s="5">
-        <v>1850.82</v>
+        <v>1836.59</v>
       </c>
       <c r="E185" s="5">
         <v>0.49</v>
       </c>
       <c r="F185" s="5">
-        <v>2313.53</v>
+        <v>2295.73</v>
       </c>
       <c r="G185" s="5">
-        <v>2961.32</v>
+        <v>2938.54</v>
       </c>
       <c r="H185" s="6" t="s">
         <v>12</v>
@@ -6721,16 +6721,16 @@
         <v>200</v>
       </c>
       <c r="D186" s="5">
-        <v>1848.27</v>
+        <v>1870.94</v>
       </c>
       <c r="E186" s="5">
         <v>0.49</v>
       </c>
       <c r="F186" s="5">
-        <v>2310.34</v>
+        <v>2338.67</v>
       </c>
       <c r="G186" s="5">
-        <v>2957.24</v>
+        <v>2993.51</v>
       </c>
       <c r="H186" s="6" t="s">
         <v>12</v>
@@ -6747,16 +6747,16 @@
         <v>200</v>
       </c>
       <c r="D187" s="5">
-        <v>1953.52</v>
+        <v>1899.34</v>
       </c>
       <c r="E187" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F187" s="5">
-        <v>2441.9</v>
+        <v>2374.17</v>
       </c>
       <c r="G187" s="5">
-        <v>3125.63</v>
+        <v>3038.94</v>
       </c>
       <c r="H187" s="6" t="s">
         <v>12</v>
@@ -6773,16 +6773,16 @@
         <v>200</v>
       </c>
       <c r="D188" s="5">
-        <v>1928.79</v>
+        <v>1904.81</v>
       </c>
       <c r="E188" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F188" s="5">
-        <v>2410.99</v>
+        <v>2381</v>
       </c>
       <c r="G188" s="5">
-        <v>3086.07</v>
+        <v>3047.69</v>
       </c>
       <c r="H188" s="6" t="s">
         <v>12</v>
@@ -6799,16 +6799,16 @@
         <v>200</v>
       </c>
       <c r="D189" s="5">
-        <v>1927.42</v>
+        <v>1939.86</v>
       </c>
       <c r="E189" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F189" s="5">
-        <v>2409.28</v>
+        <v>2424.82</v>
       </c>
       <c r="G189" s="5">
-        <v>3083.88</v>
+        <v>3103.78</v>
       </c>
       <c r="H189" s="6" t="s">
         <v>12</v>
@@ -6825,16 +6825,16 @@
         <v>200</v>
       </c>
       <c r="D190" s="5">
-        <v>1922.84</v>
+        <v>1966.01</v>
       </c>
       <c r="E190" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F190" s="5">
-        <v>2403.55</v>
+        <v>2457.51</v>
       </c>
       <c r="G190" s="5">
-        <v>3076.54</v>
+        <v>3145.61</v>
       </c>
       <c r="H190" s="6" t="s">
         <v>12</v>
@@ -6851,16 +6851,16 @@
         <v>200</v>
       </c>
       <c r="D191" s="5">
-        <v>1945.85</v>
+        <v>1953.6</v>
       </c>
       <c r="E191" s="5">
         <v>0.49</v>
       </c>
       <c r="F191" s="5">
-        <v>2432.31</v>
+        <v>2442</v>
       </c>
       <c r="G191" s="5">
-        <v>3113.37</v>
+        <v>3125.76</v>
       </c>
       <c r="H191" s="6" t="s">
         <v>12</v>
@@ -6877,16 +6877,16 @@
         <v>200</v>
       </c>
       <c r="D192" s="5">
-        <v>1994.78</v>
+        <v>1979.43</v>
       </c>
       <c r="E192" s="5">
         <v>0.49</v>
       </c>
       <c r="F192" s="5">
-        <v>2493.47</v>
+        <v>2474.29</v>
       </c>
       <c r="G192" s="5">
-        <v>3191.64</v>
+        <v>3167.09</v>
       </c>
       <c r="H192" s="6" t="s">
         <v>12</v>
@@ -6903,16 +6903,16 @@
         <v>200</v>
       </c>
       <c r="D193" s="5">
-        <v>1990.45</v>
+        <v>2014.86</v>
       </c>
       <c r="E193" s="5">
         <v>0.49</v>
       </c>
       <c r="F193" s="5">
-        <v>2488.06</v>
+        <v>2518.57</v>
       </c>
       <c r="G193" s="5">
-        <v>3184.72</v>
+        <v>3223.78</v>
       </c>
       <c r="H193" s="6" t="s">
         <v>12</v>
@@ -6929,16 +6929,16 @@
         <v>200</v>
       </c>
       <c r="D194" s="5">
-        <v>2102.16</v>
+        <v>2043.86</v>
       </c>
       <c r="E194" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F194" s="5">
-        <v>2627.7</v>
+        <v>2554.81</v>
       </c>
       <c r="G194" s="5">
-        <v>3363.45</v>
+        <v>3270.17</v>
       </c>
       <c r="H194" s="6" t="s">
         <v>12</v>
@@ -6955,16 +6955,16 @@
         <v>200</v>
       </c>
       <c r="D195" s="5">
-        <v>2073.97</v>
+        <v>2048.18</v>
       </c>
       <c r="E195" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F195" s="5">
-        <v>2592.46</v>
+        <v>2560.22</v>
       </c>
       <c r="G195" s="5">
-        <v>3318.35</v>
+        <v>3277.09</v>
       </c>
       <c r="H195" s="6" t="s">
         <v>12</v>
@@ -6981,16 +6981,16 @@
         <v>200</v>
       </c>
       <c r="D196" s="5">
-        <v>2070.95</v>
+        <v>2084.32</v>
       </c>
       <c r="E196" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F196" s="5">
-        <v>2588.69</v>
+        <v>2605.4</v>
       </c>
       <c r="G196" s="5">
-        <v>3313.53</v>
+        <v>3334.91</v>
       </c>
       <c r="H196" s="6" t="s">
         <v>12</v>
@@ -7007,16 +7007,16 @@
         <v>200</v>
       </c>
       <c r="D197" s="5">
-        <v>2064.52</v>
+        <v>2110.87</v>
       </c>
       <c r="E197" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F197" s="5">
-        <v>2580.65</v>
+        <v>2638.59</v>
       </c>
       <c r="G197" s="5">
-        <v>3303.23</v>
+        <v>3377.39</v>
       </c>
       <c r="H197" s="6" t="s">
         <v>12</v>
@@ -7033,16 +7033,16 @@
         <v>200</v>
       </c>
       <c r="D198" s="5">
-        <v>2087.74</v>
+        <v>2096.05</v>
       </c>
       <c r="E198" s="5">
         <v>0.49</v>
       </c>
       <c r="F198" s="5">
-        <v>2609.67</v>
+        <v>2620.06</v>
       </c>
       <c r="G198" s="5">
-        <v>3340.38</v>
+        <v>3353.68</v>
       </c>
       <c r="H198" s="6" t="s">
         <v>12</v>
@@ -7059,16 +7059,16 @@
         <v>200</v>
       </c>
       <c r="D199" s="5">
-        <v>2138.73</v>
+        <v>2122.28</v>
       </c>
       <c r="E199" s="5">
         <v>0.49</v>
       </c>
       <c r="F199" s="5">
-        <v>2673.41</v>
+        <v>2652.84</v>
       </c>
       <c r="G199" s="5">
-        <v>3421.96</v>
+        <v>3395.64</v>
       </c>
       <c r="H199" s="6" t="s">
         <v>12</v>
@@ -7085,16 +7085,16 @@
         <v>200</v>
       </c>
       <c r="D200" s="5">
-        <v>2132.62</v>
+        <v>2158.78</v>
       </c>
       <c r="E200" s="5">
         <v>0.49</v>
       </c>
       <c r="F200" s="5">
-        <v>2665.78</v>
+        <v>2698.47</v>
       </c>
       <c r="G200" s="5">
-        <v>3412.2</v>
+        <v>3454.05</v>
       </c>
       <c r="H200" s="6" t="s">
         <v>12</v>
@@ -7111,16 +7111,16 @@
         <v>200</v>
       </c>
       <c r="D201" s="5">
-        <v>2250.79</v>
+        <v>2188.37</v>
       </c>
       <c r="E201" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F201" s="5">
-        <v>2813.49</v>
+        <v>2735.46</v>
       </c>
       <c r="G201" s="5">
-        <v>3601.27</v>
+        <v>3501.39</v>
       </c>
       <c r="H201" s="6" t="s">
         <v>12</v>
@@ -7137,16 +7137,16 @@
         <v>200</v>
       </c>
       <c r="D202" s="5">
-        <v>2219.15</v>
+        <v>2191.55</v>
       </c>
       <c r="E202" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F202" s="5">
-        <v>2773.93</v>
+        <v>2739.44</v>
       </c>
       <c r="G202" s="5">
-        <v>3550.63</v>
+        <v>3506.49</v>
       </c>
       <c r="H202" s="6" t="s">
         <v>12</v>
@@ -7163,16 +7163,16 @@
         <v>200</v>
       </c>
       <c r="D203" s="5">
-        <v>2214.49</v>
+        <v>2228.77</v>
       </c>
       <c r="E203" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F203" s="5">
-        <v>2768.1</v>
+        <v>2785.97</v>
       </c>
       <c r="G203" s="5">
-        <v>3543.18</v>
+        <v>3566.04</v>
       </c>
       <c r="H203" s="6" t="s">
         <v>12</v>
@@ -7189,16 +7189,16 @@
         <v>200</v>
       </c>
       <c r="D204" s="5">
-        <v>2206.2</v>
+        <v>2255.73</v>
       </c>
       <c r="E204" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F204" s="5">
-        <v>2757.75</v>
+        <v>2819.67</v>
       </c>
       <c r="G204" s="5">
-        <v>3529.92</v>
+        <v>3609.18</v>
       </c>
       <c r="H204" s="6" t="s">
         <v>12</v>
@@ -7215,16 +7215,16 @@
         <v>200</v>
       </c>
       <c r="D205" s="5">
-        <v>1824.24</v>
+        <v>1831.5</v>
       </c>
       <c r="E205" s="5">
         <v>0.49</v>
       </c>
       <c r="F205" s="5">
-        <v>2280.29</v>
+        <v>2289.38</v>
       </c>
       <c r="G205" s="5">
-        <v>2918.78</v>
+        <v>2930.4</v>
       </c>
       <c r="H205" s="6" t="s">
         <v>12</v>
@@ -7241,16 +7241,16 @@
         <v>200</v>
       </c>
       <c r="D206" s="5">
-        <v>1871.39</v>
+        <v>1856.99</v>
       </c>
       <c r="E206" s="5">
         <v>0.49</v>
       </c>
       <c r="F206" s="5">
-        <v>2339.24</v>
+        <v>2321.24</v>
       </c>
       <c r="G206" s="5">
-        <v>2994.22</v>
+        <v>2971.19</v>
       </c>
       <c r="H206" s="6" t="s">
         <v>12</v>
@@ -7267,16 +7267,16 @@
         <v>200</v>
       </c>
       <c r="D207" s="5">
-        <v>1868.58</v>
+        <v>1891.5</v>
       </c>
       <c r="E207" s="5">
         <v>0.49</v>
       </c>
       <c r="F207" s="5">
-        <v>2335.73</v>
+        <v>2364.37</v>
       </c>
       <c r="G207" s="5">
-        <v>2989.73</v>
+        <v>3026.4</v>
       </c>
       <c r="H207" s="6" t="s">
         <v>12</v>
@@ -7293,16 +7293,16 @@
         <v>200</v>
       </c>
       <c r="D208" s="5">
-        <v>1974.75</v>
+        <v>1919.99</v>
       </c>
       <c r="E208" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F208" s="5">
-        <v>2468.44</v>
+        <v>2399.98</v>
       </c>
       <c r="G208" s="5">
-        <v>3159.6</v>
+        <v>3071.98</v>
       </c>
       <c r="H208" s="6" t="s">
         <v>12</v>
@@ -7319,16 +7319,16 @@
         <v>200</v>
       </c>
       <c r="D209" s="5">
-        <v>1949.53</v>
+        <v>1925.29</v>
       </c>
       <c r="E209" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F209" s="5">
-        <v>2436.91</v>
+        <v>2406.61</v>
       </c>
       <c r="G209" s="5">
-        <v>3119.25</v>
+        <v>3080.46</v>
       </c>
       <c r="H209" s="6" t="s">
         <v>12</v>
@@ -7345,16 +7345,16 @@
         <v>200</v>
       </c>
       <c r="D210" s="5">
-        <v>1947.93</v>
+        <v>1960.5</v>
       </c>
       <c r="E210" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F210" s="5">
-        <v>2434.91</v>
+        <v>2450.62</v>
       </c>
       <c r="G210" s="5">
-        <v>3116.68</v>
+        <v>3136.8</v>
       </c>
       <c r="H210" s="6" t="s">
         <v>12</v>
@@ -7371,16 +7371,16 @@
         <v>200</v>
       </c>
       <c r="D211" s="5">
-        <v>1943.08</v>
+        <v>1986.7</v>
       </c>
       <c r="E211" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F211" s="5">
-        <v>2428.85</v>
+        <v>2483.38</v>
       </c>
       <c r="G211" s="5">
-        <v>3108.92</v>
+        <v>3178.72</v>
       </c>
       <c r="H211" s="6" t="s">
         <v>12</v>
@@ -7397,16 +7397,16 @@
         <v>200</v>
       </c>
       <c r="D212" s="5">
-        <v>1966.12</v>
+        <v>1973.95</v>
       </c>
       <c r="E212" s="5">
         <v>0.49</v>
       </c>
       <c r="F212" s="5">
-        <v>2457.65</v>
+        <v>2467.44</v>
       </c>
       <c r="G212" s="5">
-        <v>3145.8</v>
+        <v>3158.32</v>
       </c>
       <c r="H212" s="6" t="s">
         <v>12</v>
@@ -7423,16 +7423,16 @@
         <v>200</v>
       </c>
       <c r="D213" s="5">
-        <v>2015.34</v>
+        <v>1999.84</v>
       </c>
       <c r="E213" s="5">
         <v>0.49</v>
       </c>
       <c r="F213" s="5">
-        <v>2519.18</v>
+        <v>2499.79</v>
       </c>
       <c r="G213" s="5">
-        <v>3224.54</v>
+        <v>3199.74</v>
       </c>
       <c r="H213" s="6" t="s">
         <v>12</v>
@@ -7449,16 +7449,16 @@
         <v>200</v>
       </c>
       <c r="D214" s="5">
-        <v>2010.76</v>
+        <v>2035.42</v>
       </c>
       <c r="E214" s="5">
         <v>0.49</v>
       </c>
       <c r="F214" s="5">
-        <v>2513.45</v>
+        <v>2544.27</v>
       </c>
       <c r="G214" s="5">
-        <v>3217.21</v>
+        <v>3256.67</v>
       </c>
       <c r="H214" s="6" t="s">
         <v>12</v>
@@ -7475,16 +7475,16 @@
         <v>200</v>
       </c>
       <c r="D215" s="5">
-        <v>2123.39</v>
+        <v>2064.5</v>
       </c>
       <c r="E215" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F215" s="5">
-        <v>2654.24</v>
+        <v>2580.62</v>
       </c>
       <c r="G215" s="5">
-        <v>3397.42</v>
+        <v>3303.2</v>
       </c>
       <c r="H215" s="6" t="s">
         <v>12</v>
@@ -7501,16 +7501,16 @@
         <v>200</v>
       </c>
       <c r="D216" s="5">
-        <v>2094.71</v>
+        <v>2068.66</v>
       </c>
       <c r="E216" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F216" s="5">
-        <v>2618.38</v>
+        <v>2585.82</v>
       </c>
       <c r="G216" s="5">
-        <v>3351.53</v>
+        <v>3309.86</v>
       </c>
       <c r="H216" s="6" t="s">
         <v>12</v>
@@ -7527,16 +7527,16 @@
         <v>200</v>
       </c>
       <c r="D217" s="5">
-        <v>2091.46</v>
+        <v>2104.95</v>
       </c>
       <c r="E217" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F217" s="5">
-        <v>2614.32</v>
+        <v>2631.19</v>
       </c>
       <c r="G217" s="5">
-        <v>3346.33</v>
+        <v>3367.93</v>
       </c>
       <c r="H217" s="6" t="s">
         <v>12</v>
@@ -7553,16 +7553,16 @@
         <v>200</v>
       </c>
       <c r="D218" s="5">
-        <v>2084.76</v>
+        <v>2131.56</v>
       </c>
       <c r="E218" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F218" s="5">
-        <v>2605.95</v>
+        <v>2664.46</v>
       </c>
       <c r="G218" s="5">
-        <v>3335.61</v>
+        <v>3410.51</v>
       </c>
       <c r="H218" s="6" t="s">
         <v>12</v>
@@ -7579,16 +7579,16 @@
         <v>200</v>
       </c>
       <c r="D219" s="5">
-        <v>2108.01</v>
+        <v>2116.4</v>
       </c>
       <c r="E219" s="5">
         <v>0.49</v>
       </c>
       <c r="F219" s="5">
-        <v>2635.01</v>
+        <v>2645.5</v>
       </c>
       <c r="G219" s="5">
-        <v>3372.81</v>
+        <v>3386.24</v>
       </c>
       <c r="H219" s="6" t="s">
         <v>12</v>
@@ -7605,16 +7605,16 @@
         <v>200</v>
       </c>
       <c r="D220" s="5">
-        <v>2159.29</v>
+        <v>2142.68</v>
       </c>
       <c r="E220" s="5">
         <v>0.49</v>
       </c>
       <c r="F220" s="5">
-        <v>2699.12</v>
+        <v>2678.35</v>
       </c>
       <c r="G220" s="5">
-        <v>3454.87</v>
+        <v>3428.29</v>
       </c>
       <c r="H220" s="6" t="s">
         <v>12</v>
@@ -7631,16 +7631,16 @@
         <v>200</v>
       </c>
       <c r="D221" s="5">
-        <v>2152.93</v>
+        <v>2179.34</v>
       </c>
       <c r="E221" s="5">
         <v>0.49</v>
       </c>
       <c r="F221" s="5">
-        <v>2691.17</v>
+        <v>2724.17</v>
       </c>
       <c r="G221" s="5">
-        <v>3444.69</v>
+        <v>3486.94</v>
       </c>
       <c r="H221" s="6" t="s">
         <v>12</v>
@@ -7657,16 +7657,16 @@
         <v>200</v>
       </c>
       <c r="D222" s="5">
-        <v>2272.03</v>
+        <v>2209.02</v>
       </c>
       <c r="E222" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F222" s="5">
-        <v>2840.04</v>
+        <v>2761.26</v>
       </c>
       <c r="G222" s="5">
-        <v>3635.24</v>
+        <v>3534.42</v>
       </c>
       <c r="H222" s="6" t="s">
         <v>12</v>
@@ -7683,16 +7683,16 @@
         <v>200</v>
       </c>
       <c r="D223" s="5">
-        <v>2239.89</v>
+        <v>2212.03</v>
       </c>
       <c r="E223" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F223" s="5">
-        <v>2799.86</v>
+        <v>2765.04</v>
       </c>
       <c r="G223" s="5">
-        <v>3583.82</v>
+        <v>3539.26</v>
       </c>
       <c r="H223" s="6" t="s">
         <v>12</v>
@@ -7709,16 +7709,16 @@
         <v>200</v>
       </c>
       <c r="D224" s="5">
-        <v>2234.99</v>
+        <v>2249.41</v>
       </c>
       <c r="E224" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F224" s="5">
-        <v>2793.74</v>
+        <v>2811.76</v>
       </c>
       <c r="G224" s="5">
-        <v>3575.98</v>
+        <v>3599.06</v>
       </c>
       <c r="H224" s="6" t="s">
         <v>12</v>
@@ -7735,16 +7735,16 @@
         <v>200</v>
       </c>
       <c r="D225" s="5">
-        <v>1821.64</v>
+        <v>1862.53</v>
       </c>
       <c r="E225" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F225" s="5">
-        <v>2277.05</v>
+        <v>2328.16</v>
       </c>
       <c r="G225" s="5">
-        <v>2914.61</v>
+        <v>2980.05</v>
       </c>
       <c r="H225" s="6" t="s">
         <v>12</v>
@@ -7761,16 +7761,16 @@
         <v>200</v>
       </c>
       <c r="D226" s="5">
-        <v>1844.51</v>
+        <v>1851.85</v>
       </c>
       <c r="E226" s="5">
         <v>0.49</v>
       </c>
       <c r="F226" s="5">
-        <v>2305.63</v>
+        <v>2314.81</v>
       </c>
       <c r="G226" s="5">
-        <v>2951.21</v>
+        <v>2962.96</v>
       </c>
       <c r="H226" s="6" t="s">
         <v>12</v>
@@ -7787,16 +7787,16 @@
         <v>200</v>
       </c>
       <c r="D227" s="5">
-        <v>1891.95</v>
+        <v>1877.4</v>
       </c>
       <c r="E227" s="5">
         <v>0.49</v>
       </c>
       <c r="F227" s="5">
-        <v>2364.94</v>
+        <v>2346.75</v>
       </c>
       <c r="G227" s="5">
-        <v>3027.12</v>
+        <v>3003.84</v>
       </c>
       <c r="H227" s="6" t="s">
         <v>12</v>
@@ -7813,16 +7813,16 @@
         <v>200</v>
       </c>
       <c r="D228" s="5">
-        <v>1888.9</v>
+        <v>1912.06</v>
       </c>
       <c r="E228" s="5">
         <v>0.49</v>
       </c>
       <c r="F228" s="5">
-        <v>2361.12</v>
+        <v>2390.07</v>
       </c>
       <c r="G228" s="5">
-        <v>3022.23</v>
+        <v>3059.3</v>
       </c>
       <c r="H228" s="6" t="s">
         <v>12</v>
@@ -7839,16 +7839,16 @@
         <v>200</v>
       </c>
       <c r="D229" s="5">
-        <v>1995.99</v>
+        <v>1940.63</v>
       </c>
       <c r="E229" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F229" s="5">
-        <v>2494.99</v>
+        <v>2425.78</v>
       </c>
       <c r="G229" s="5">
-        <v>3193.57</v>
+        <v>3105.01</v>
       </c>
       <c r="H229" s="6" t="s">
         <v>12</v>
@@ -7865,16 +7865,16 @@
         <v>200</v>
       </c>
       <c r="D230" s="5">
-        <v>1970.27</v>
+        <v>1945.77</v>
       </c>
       <c r="E230" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F230" s="5">
-        <v>2462.84</v>
+        <v>2432.21</v>
       </c>
       <c r="G230" s="5">
-        <v>3152.43</v>
+        <v>3113.24</v>
       </c>
       <c r="H230" s="6" t="s">
         <v>12</v>
@@ -7891,16 +7891,16 @@
         <v>200</v>
       </c>
       <c r="D231" s="5">
-        <v>1968.43</v>
+        <v>1981.13</v>
       </c>
       <c r="E231" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F231" s="5">
-        <v>2460.54</v>
+        <v>2476.42</v>
       </c>
       <c r="G231" s="5">
-        <v>3149.49</v>
+        <v>3169.81</v>
       </c>
       <c r="H231" s="6" t="s">
         <v>12</v>
@@ -7917,16 +7917,16 @@
         <v>200</v>
       </c>
       <c r="D232" s="5">
-        <v>1963.32</v>
+        <v>2007.4</v>
       </c>
       <c r="E232" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F232" s="5">
-        <v>2454.15</v>
+        <v>2509.24</v>
       </c>
       <c r="G232" s="5">
-        <v>3141.31</v>
+        <v>3211.83</v>
       </c>
       <c r="H232" s="6" t="s">
         <v>12</v>
@@ -7943,16 +7943,16 @@
         <v>200</v>
       </c>
       <c r="D233" s="5">
-        <v>1986.39</v>
+        <v>1994.3</v>
       </c>
       <c r="E233" s="5">
         <v>0.49</v>
       </c>
       <c r="F233" s="5">
-        <v>2482.99</v>
+        <v>2492.88</v>
       </c>
       <c r="G233" s="5">
-        <v>3178.23</v>
+        <v>3190.88</v>
       </c>
       <c r="H233" s="6" t="s">
         <v>12</v>
@@ -7969,16 +7969,16 @@
         <v>200</v>
       </c>
       <c r="D234" s="5">
-        <v>2035.91</v>
+        <v>2020.24</v>
       </c>
       <c r="E234" s="5">
         <v>0.49</v>
       </c>
       <c r="F234" s="5">
-        <v>2544.88</v>
+        <v>2525.3</v>
       </c>
       <c r="G234" s="5">
-        <v>3257.45</v>
+        <v>3232.39</v>
       </c>
       <c r="H234" s="6" t="s">
         <v>12</v>
@@ -7995,16 +7995,16 @@
         <v>200</v>
       </c>
       <c r="D235" s="5">
-        <v>2031.07</v>
+        <v>2055.98</v>
       </c>
       <c r="E235" s="5">
         <v>0.49</v>
       </c>
       <c r="F235" s="5">
-        <v>2538.84</v>
+        <v>2569.97</v>
       </c>
       <c r="G235" s="5">
-        <v>3249.71</v>
+        <v>3289.57</v>
       </c>
       <c r="H235" s="6" t="s">
         <v>12</v>
@@ -8021,16 +8021,16 @@
         <v>200</v>
       </c>
       <c r="D236" s="5">
-        <v>2144.62</v>
+        <v>2085.14</v>
       </c>
       <c r="E236" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F236" s="5">
-        <v>2680.78</v>
+        <v>2606.43</v>
       </c>
       <c r="G236" s="5">
-        <v>3431.39</v>
+        <v>3336.23</v>
       </c>
       <c r="H236" s="6" t="s">
         <v>12</v>
@@ -8047,16 +8047,16 @@
         <v>200</v>
       </c>
       <c r="D237" s="5">
-        <v>2115.45</v>
+        <v>2089.14</v>
       </c>
       <c r="E237" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F237" s="5">
-        <v>2644.31</v>
+        <v>2611.42</v>
       </c>
       <c r="G237" s="5">
-        <v>3384.72</v>
+        <v>3342.63</v>
       </c>
       <c r="H237" s="6" t="s">
         <v>12</v>
@@ -8073,16 +8073,16 @@
         <v>200</v>
       </c>
       <c r="D238" s="5">
-        <v>2111.96</v>
+        <v>2125.59</v>
       </c>
       <c r="E238" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F238" s="5">
-        <v>2639.95</v>
+        <v>2656.99</v>
       </c>
       <c r="G238" s="5">
-        <v>3379.14</v>
+        <v>3400.95</v>
       </c>
       <c r="H238" s="6" t="s">
         <v>12</v>
@@ -8099,16 +8099,16 @@
         <v>200</v>
       </c>
       <c r="D239" s="5">
-        <v>2105</v>
+        <v>2152.26</v>
       </c>
       <c r="E239" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F239" s="5">
-        <v>2631.25</v>
+        <v>2690.32</v>
       </c>
       <c r="G239" s="5">
-        <v>3368</v>
+        <v>3443.62</v>
       </c>
       <c r="H239" s="6" t="s">
         <v>12</v>
@@ -8125,16 +8125,16 @@
         <v>200</v>
       </c>
       <c r="D240" s="5">
-        <v>2128.28</v>
+        <v>2136.75</v>
       </c>
       <c r="E240" s="5">
         <v>0.49</v>
       </c>
       <c r="F240" s="5">
-        <v>2660.34</v>
+        <v>2670.94</v>
       </c>
       <c r="G240" s="5">
-        <v>3405.24</v>
+        <v>3418.8</v>
       </c>
       <c r="H240" s="6" t="s">
         <v>12</v>
@@ -8151,16 +8151,16 @@
         <v>200</v>
       </c>
       <c r="D241" s="5">
-        <v>2179.86</v>
+        <v>2163.09</v>
       </c>
       <c r="E241" s="5">
         <v>0.49</v>
       </c>
       <c r="F241" s="5">
-        <v>2724.83</v>
+        <v>2703.86</v>
       </c>
       <c r="G241" s="5">
-        <v>3487.77</v>
+        <v>3460.94</v>
       </c>
       <c r="H241" s="6" t="s">
         <v>12</v>
@@ -8177,16 +8177,16 @@
         <v>200</v>
       </c>
       <c r="D242" s="5">
-        <v>2173.24</v>
+        <v>2199.9</v>
       </c>
       <c r="E242" s="5">
         <v>0.49</v>
       </c>
       <c r="F242" s="5">
-        <v>2716.56</v>
+        <v>2749.87</v>
       </c>
       <c r="G242" s="5">
-        <v>3477.19</v>
+        <v>3519.84</v>
       </c>
       <c r="H242" s="6" t="s">
         <v>12</v>
@@ -8203,16 +8203,16 @@
         <v>200</v>
       </c>
       <c r="D243" s="5">
-        <v>2293.26</v>
+        <v>2229.66</v>
       </c>
       <c r="E243" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F243" s="5">
-        <v>2866.58</v>
+        <v>2787.07</v>
       </c>
       <c r="G243" s="5">
-        <v>3669.21</v>
+        <v>3567.46</v>
       </c>
       <c r="H243" s="6" t="s">
         <v>12</v>
@@ -8229,16 +8229,16 @@
         <v>200</v>
       </c>
       <c r="D244" s="5">
-        <v>2260.63</v>
+        <v>2232.52</v>
       </c>
       <c r="E244" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F244" s="5">
-        <v>2825.78</v>
+        <v>2790.64</v>
       </c>
       <c r="G244" s="5">
-        <v>3617</v>
+        <v>3572.03</v>
       </c>
       <c r="H244" s="6" t="s">
         <v>12</v>
@@ -8255,16 +8255,16 @@
         <v>200</v>
       </c>
       <c r="D245" s="5">
-        <v>1845.4</v>
+        <v>1857.31</v>
       </c>
       <c r="E245" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F245" s="5">
-        <v>2306.75</v>
+        <v>2321.64</v>
       </c>
       <c r="G245" s="5">
-        <v>2952.65</v>
+        <v>2971.7</v>
       </c>
       <c r="H245" s="6" t="s">
         <v>12</v>
@@ -8281,16 +8281,16 @@
         <v>200</v>
       </c>
       <c r="D246" s="5">
-        <v>1841.88</v>
+        <v>1883.23</v>
       </c>
       <c r="E246" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F246" s="5">
-        <v>2302.35</v>
+        <v>2354.03</v>
       </c>
       <c r="G246" s="5">
-        <v>2947</v>
+        <v>3013.16</v>
       </c>
       <c r="H246" s="6" t="s">
         <v>12</v>
@@ -8307,16 +8307,16 @@
         <v>200</v>
       </c>
       <c r="D247" s="5">
-        <v>1864.78</v>
+        <v>1872.2</v>
       </c>
       <c r="E247" s="5">
         <v>0.49</v>
       </c>
       <c r="F247" s="5">
-        <v>2330.97</v>
+        <v>2340.25</v>
       </c>
       <c r="G247" s="5">
-        <v>2983.64</v>
+        <v>2995.52</v>
       </c>
       <c r="H247" s="6" t="s">
         <v>12</v>
@@ -8333,16 +8333,16 @@
         <v>200</v>
       </c>
       <c r="D248" s="5">
-        <v>1912.52</v>
+        <v>1897.8</v>
       </c>
       <c r="E248" s="5">
         <v>0.49</v>
       </c>
       <c r="F248" s="5">
-        <v>2390.65</v>
+        <v>2372.25</v>
       </c>
       <c r="G248" s="5">
-        <v>3060.03</v>
+        <v>3036.49</v>
       </c>
       <c r="H248" s="6" t="s">
         <v>12</v>
@@ -8359,16 +8359,16 @@
         <v>200</v>
       </c>
       <c r="D249" s="5">
-        <v>1909.21</v>
+        <v>1932.62</v>
       </c>
       <c r="E249" s="5">
         <v>0.49</v>
       </c>
       <c r="F249" s="5">
-        <v>2386.51</v>
+        <v>2415.77</v>
       </c>
       <c r="G249" s="5">
-        <v>3054.73</v>
+        <v>3092.2</v>
       </c>
       <c r="H249" s="6" t="s">
         <v>12</v>
@@ -8385,16 +8385,16 @@
         <v>200</v>
       </c>
       <c r="D250" s="5">
-        <v>2017.22</v>
+        <v>1961.28</v>
       </c>
       <c r="E250" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F250" s="5">
-        <v>2521.53</v>
+        <v>2451.59</v>
       </c>
       <c r="G250" s="5">
-        <v>3227.55</v>
+        <v>3138.04</v>
       </c>
       <c r="H250" s="6" t="s">
         <v>12</v>
@@ -8411,16 +8411,16 @@
         <v>200</v>
       </c>
       <c r="D251" s="5">
-        <v>1991.01</v>
+        <v>1966.25</v>
       </c>
       <c r="E251" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F251" s="5">
-        <v>2488.76</v>
+        <v>2457.81</v>
       </c>
       <c r="G251" s="5">
-        <v>3185.62</v>
+        <v>3146.01</v>
       </c>
       <c r="H251" s="6" t="s">
         <v>12</v>
@@ -8437,16 +8437,16 @@
         <v>200</v>
       </c>
       <c r="D252" s="5">
-        <v>1988.94</v>
+        <v>2001.77</v>
       </c>
       <c r="E252" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F252" s="5">
-        <v>2486.17</v>
+        <v>2502.21</v>
       </c>
       <c r="G252" s="5">
-        <v>3182.3</v>
+        <v>3202.83</v>
       </c>
       <c r="H252" s="6" t="s">
         <v>12</v>
@@ -8463,16 +8463,16 @@
         <v>200</v>
       </c>
       <c r="D253" s="5">
-        <v>1983.56</v>
+        <v>2028.09</v>
       </c>
       <c r="E253" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F253" s="5">
-        <v>2479.45</v>
+        <v>2535.11</v>
       </c>
       <c r="G253" s="5">
-        <v>3173.69</v>
+        <v>3244.95</v>
       </c>
       <c r="H253" s="6" t="s">
         <v>12</v>
@@ -8489,16 +8489,16 @@
         <v>200</v>
       </c>
       <c r="D254" s="5">
-        <v>2006.66</v>
+        <v>2014.65</v>
       </c>
       <c r="E254" s="5">
         <v>0.49</v>
       </c>
       <c r="F254" s="5">
-        <v>2508.32</v>
+        <v>2518.31</v>
       </c>
       <c r="G254" s="5">
-        <v>3210.66</v>
+        <v>3223.44</v>
       </c>
       <c r="H254" s="6" t="s">
         <v>12</v>
@@ -8515,16 +8515,16 @@
         <v>200</v>
       </c>
       <c r="D255" s="5">
-        <v>2056.47</v>
+        <v>2040.65</v>
       </c>
       <c r="E255" s="5">
         <v>0.49</v>
       </c>
       <c r="F255" s="5">
-        <v>2570.59</v>
+        <v>2550.81</v>
       </c>
       <c r="G255" s="5">
-        <v>3290.35</v>
+        <v>3265.04</v>
       </c>
       <c r="H255" s="6" t="s">
         <v>12</v>
@@ -8541,16 +8541,16 @@
         <v>200</v>
       </c>
       <c r="D256" s="5">
-        <v>2051.38</v>
+        <v>2076.54</v>
       </c>
       <c r="E256" s="5">
         <v>0.49</v>
       </c>
       <c r="F256" s="5">
-        <v>2564.23</v>
+        <v>2595.67</v>
       </c>
       <c r="G256" s="5">
-        <v>3282.21</v>
+        <v>3322.47</v>
       </c>
       <c r="H256" s="6" t="s">
         <v>12</v>
@@ -8567,16 +8567,16 @@
         <v>200</v>
       </c>
       <c r="D257" s="5">
-        <v>2165.86</v>
+        <v>2105.79</v>
       </c>
       <c r="E257" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F257" s="5">
-        <v>2707.32</v>
+        <v>2632.23</v>
       </c>
       <c r="G257" s="5">
-        <v>3465.37</v>
+        <v>3369.26</v>
       </c>
       <c r="H257" s="6" t="s">
         <v>12</v>
@@ -8593,16 +8593,16 @@
         <v>200</v>
       </c>
       <c r="D258" s="5">
-        <v>2136.19</v>
+        <v>2109.63</v>
       </c>
       <c r="E258" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F258" s="5">
-        <v>2670.23</v>
+        <v>2637.03</v>
       </c>
       <c r="G258" s="5">
-        <v>3417.9</v>
+        <v>3375.4</v>
       </c>
       <c r="H258" s="6" t="s">
         <v>12</v>
@@ -8619,16 +8619,16 @@
         <v>200</v>
       </c>
       <c r="D259" s="5">
-        <v>2132.47</v>
+        <v>2146.23</v>
       </c>
       <c r="E259" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F259" s="5">
-        <v>2665.58</v>
+        <v>2682.78</v>
       </c>
       <c r="G259" s="5">
-        <v>3411.95</v>
+        <v>3433.97</v>
       </c>
       <c r="H259" s="6" t="s">
         <v>12</v>
@@ -8645,16 +8645,16 @@
         <v>200</v>
       </c>
       <c r="D260" s="5">
-        <v>2125.24</v>
+        <v>2172.95</v>
       </c>
       <c r="E260" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F260" s="5">
-        <v>2656.55</v>
+        <v>2716.19</v>
       </c>
       <c r="G260" s="5">
-        <v>3400.38</v>
+        <v>3476.73</v>
       </c>
       <c r="H260" s="6" t="s">
         <v>12</v>
@@ -8671,16 +8671,16 @@
         <v>200</v>
       </c>
       <c r="D261" s="5">
-        <v>2148.55</v>
+        <v>2157.1</v>
       </c>
       <c r="E261" s="5">
         <v>0.49</v>
       </c>
       <c r="F261" s="5">
-        <v>2685.68</v>
+        <v>2696.38</v>
       </c>
       <c r="G261" s="5">
-        <v>3437.68</v>
+        <v>3451.36</v>
       </c>
       <c r="H261" s="6" t="s">
         <v>12</v>
@@ -8697,16 +8697,16 @@
         <v>200</v>
       </c>
       <c r="D262" s="5">
-        <v>2200.42</v>
+        <v>2183.5</v>
       </c>
       <c r="E262" s="5">
         <v>0.49</v>
       </c>
       <c r="F262" s="5">
-        <v>2750.53</v>
+        <v>2729.37</v>
       </c>
       <c r="G262" s="5">
-        <v>3520.67</v>
+        <v>3493.59</v>
       </c>
       <c r="H262" s="6" t="s">
         <v>12</v>
@@ -8723,16 +8723,16 @@
         <v>200</v>
       </c>
       <c r="D263" s="5">
-        <v>2193.56</v>
+        <v>2220.46</v>
       </c>
       <c r="E263" s="5">
         <v>0.49</v>
       </c>
       <c r="F263" s="5">
-        <v>2741.95</v>
+        <v>2775.57</v>
       </c>
       <c r="G263" s="5">
-        <v>3509.69</v>
+        <v>3552.74</v>
       </c>
       <c r="H263" s="6" t="s">
         <v>12</v>
@@ -8749,16 +8749,16 @@
         <v>200</v>
       </c>
       <c r="D264" s="5">
-        <v>2314.5</v>
+        <v>2250.31</v>
       </c>
       <c r="E264" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F264" s="5">
-        <v>2893.12</v>
+        <v>2812.88</v>
       </c>
       <c r="G264" s="5">
-        <v>3703.19</v>
+        <v>3600.49</v>
       </c>
       <c r="H264" s="6" t="s">
         <v>12</v>
@@ -8775,16 +8775,16 @@
         <v>200</v>
       </c>
       <c r="D265" s="5">
-        <v>1866.57</v>
+        <v>1843.36</v>
       </c>
       <c r="E265" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F265" s="5">
-        <v>2333.21</v>
+        <v>2304.2</v>
       </c>
       <c r="G265" s="5">
-        <v>2986.51</v>
+        <v>2949.38</v>
       </c>
       <c r="H265" s="6" t="s">
         <v>12</v>
@@ -8801,16 +8801,16 @@
         <v>200</v>
       </c>
       <c r="D266" s="5">
-        <v>1865.91</v>
+        <v>1877.95</v>
       </c>
       <c r="E266" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F266" s="5">
-        <v>2332.38</v>
+        <v>2347.44</v>
       </c>
       <c r="G266" s="5">
-        <v>2985.46</v>
+        <v>3004.72</v>
       </c>
       <c r="H266" s="6" t="s">
         <v>12</v>
@@ -8827,16 +8827,16 @@
         <v>200</v>
       </c>
       <c r="D267" s="5">
-        <v>1862.12</v>
+        <v>1903.92</v>
       </c>
       <c r="E267" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F267" s="5">
-        <v>2327.65</v>
+        <v>2379.9</v>
       </c>
       <c r="G267" s="5">
-        <v>2979.38</v>
+        <v>3046.28</v>
       </c>
       <c r="H267" s="6" t="s">
         <v>12</v>
@@ -8853,16 +8853,16 @@
         <v>200</v>
       </c>
       <c r="D268" s="5">
-        <v>1885.04</v>
+        <v>1892.55</v>
       </c>
       <c r="E268" s="5">
         <v>0.49</v>
       </c>
       <c r="F268" s="5">
-        <v>2356.3</v>
+        <v>2365.69</v>
       </c>
       <c r="G268" s="5">
-        <v>3016.07</v>
+        <v>3028.08</v>
       </c>
       <c r="H268" s="6" t="s">
         <v>12</v>
@@ -8879,16 +8879,16 @@
         <v>200</v>
       </c>
       <c r="D269" s="5">
-        <v>1933.08</v>
+        <v>1918.21</v>
       </c>
       <c r="E269" s="5">
         <v>0.49</v>
       </c>
       <c r="F269" s="5">
-        <v>2416.35</v>
+        <v>2397.76</v>
       </c>
       <c r="G269" s="5">
-        <v>3092.93</v>
+        <v>3069.14</v>
       </c>
       <c r="H269" s="6" t="s">
         <v>12</v>
@@ -8905,16 +8905,16 @@
         <v>200</v>
       </c>
       <c r="D270" s="5">
-        <v>1929.52</v>
+        <v>1953.18</v>
       </c>
       <c r="E270" s="5">
         <v>0.49</v>
       </c>
       <c r="F270" s="5">
-        <v>2411.9</v>
+        <v>2441.47</v>
       </c>
       <c r="G270" s="5">
-        <v>3087.22</v>
+        <v>3125.09</v>
       </c>
       <c r="H270" s="6" t="s">
         <v>12</v>
@@ -8931,16 +8931,16 @@
         <v>200</v>
       </c>
       <c r="D271" s="5">
-        <v>2038.45</v>
+        <v>1981.92</v>
       </c>
       <c r="E271" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F271" s="5">
-        <v>2548.07</v>
+        <v>2477.4</v>
       </c>
       <c r="G271" s="5">
-        <v>3261.52</v>
+        <v>3171.07</v>
       </c>
       <c r="H271" s="6" t="s">
         <v>12</v>
@@ -8957,16 +8957,16 @@
         <v>200</v>
       </c>
       <c r="D272" s="5">
-        <v>2011.75</v>
+        <v>1986.73</v>
       </c>
       <c r="E272" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F272" s="5">
-        <v>2514.69</v>
+        <v>2483.41</v>
       </c>
       <c r="G272" s="5">
-        <v>3218.8</v>
+        <v>3178.78</v>
       </c>
       <c r="H272" s="6" t="s">
         <v>12</v>
@@ -8983,16 +8983,16 @@
         <v>200</v>
       </c>
       <c r="D273" s="5">
-        <v>2009.44</v>
+        <v>2022.41</v>
       </c>
       <c r="E273" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F273" s="5">
-        <v>2511.8</v>
+        <v>2528.01</v>
       </c>
       <c r="G273" s="5">
-        <v>3215.11</v>
+        <v>3235.85</v>
       </c>
       <c r="H273" s="6" t="s">
         <v>12</v>
@@ -9009,16 +9009,16 @@
         <v>200</v>
       </c>
       <c r="D274" s="5">
-        <v>2003.8</v>
+        <v>2048.79</v>
       </c>
       <c r="E274" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F274" s="5">
-        <v>2504.75</v>
+        <v>2560.98</v>
       </c>
       <c r="G274" s="5">
-        <v>3206.08</v>
+        <v>3278.06</v>
       </c>
       <c r="H274" s="6" t="s">
         <v>12</v>
@@ -9035,16 +9035,16 @@
         <v>200</v>
       </c>
       <c r="D275" s="5">
-        <v>2026.93</v>
+        <v>2035</v>
       </c>
       <c r="E275" s="5">
         <v>0.49</v>
       </c>
       <c r="F275" s="5">
-        <v>2533.66</v>
+        <v>2543.75</v>
       </c>
       <c r="G275" s="5">
-        <v>3243.09</v>
+        <v>3256</v>
       </c>
       <c r="H275" s="6" t="s">
         <v>12</v>
@@ -9061,16 +9061,16 @@
         <v>200</v>
       </c>
       <c r="D276" s="5">
-        <v>2077.03</v>
+        <v>2061.06</v>
       </c>
       <c r="E276" s="5">
         <v>0.49</v>
       </c>
       <c r="F276" s="5">
-        <v>2596.3</v>
+        <v>2576.32</v>
       </c>
       <c r="G276" s="5">
-        <v>3323.25</v>
+        <v>3297.69</v>
       </c>
       <c r="H276" s="6" t="s">
         <v>12</v>
@@ -9087,16 +9087,16 @@
         <v>200</v>
       </c>
       <c r="D277" s="5">
-        <v>2071.69</v>
+        <v>2097.1</v>
       </c>
       <c r="E277" s="5">
         <v>0.49</v>
       </c>
       <c r="F277" s="5">
-        <v>2589.62</v>
+        <v>2621.37</v>
       </c>
       <c r="G277" s="5">
-        <v>3314.7</v>
+        <v>3355.36</v>
       </c>
       <c r="H277" s="6" t="s">
         <v>12</v>
@@ -9113,16 +9113,16 @@
         <v>200</v>
       </c>
       <c r="D278" s="5">
-        <v>2187.09</v>
+        <v>2126.43</v>
       </c>
       <c r="E278" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F278" s="5">
-        <v>2733.87</v>
+        <v>2658.04</v>
       </c>
       <c r="G278" s="5">
-        <v>3499.34</v>
+        <v>3402.3</v>
       </c>
       <c r="H278" s="6" t="s">
         <v>12</v>
@@ -9139,16 +9139,16 @@
         <v>200</v>
       </c>
       <c r="D279" s="5">
-        <v>2156.93</v>
+        <v>2130.11</v>
       </c>
       <c r="E279" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F279" s="5">
-        <v>2696.16</v>
+        <v>2662.63</v>
       </c>
       <c r="G279" s="5">
-        <v>3451.08</v>
+        <v>3408.17</v>
       </c>
       <c r="H279" s="6" t="s">
         <v>12</v>
@@ -9165,16 +9165,16 @@
         <v>200</v>
       </c>
       <c r="D280" s="5">
-        <v>2152.97</v>
+        <v>2166.86</v>
       </c>
       <c r="E280" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F280" s="5">
-        <v>2691.21</v>
+        <v>2708.58</v>
       </c>
       <c r="G280" s="5">
-        <v>3444.76</v>
+        <v>3466.98</v>
       </c>
       <c r="H280" s="6" t="s">
         <v>12</v>
@@ -9191,16 +9191,16 @@
         <v>200</v>
       </c>
       <c r="D281" s="5">
-        <v>2145.48</v>
+        <v>2193.65</v>
       </c>
       <c r="E281" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F281" s="5">
-        <v>2681.85</v>
+        <v>2742.06</v>
       </c>
       <c r="G281" s="5">
-        <v>3432.77</v>
+        <v>3509.84</v>
       </c>
       <c r="H281" s="6" t="s">
         <v>12</v>
@@ -9217,16 +9217,16 @@
         <v>200</v>
       </c>
       <c r="D282" s="5">
-        <v>2168.82</v>
+        <v>2177.45</v>
       </c>
       <c r="E282" s="5">
         <v>0.49</v>
       </c>
       <c r="F282" s="5">
-        <v>2711.02</v>
+        <v>2721.81</v>
       </c>
       <c r="G282" s="5">
-        <v>3470.11</v>
+        <v>3483.92</v>
       </c>
       <c r="H282" s="6" t="s">
         <v>12</v>
@@ -9243,16 +9243,16 @@
         <v>200</v>
       </c>
       <c r="D283" s="5">
-        <v>2220.99</v>
+        <v>2203.9</v>
       </c>
       <c r="E283" s="5">
         <v>0.49</v>
       </c>
       <c r="F283" s="5">
-        <v>2776.24</v>
+        <v>2754.87</v>
       </c>
       <c r="G283" s="5">
-        <v>3553.58</v>
+        <v>3526.24</v>
       </c>
       <c r="H283" s="6" t="s">
         <v>12</v>
@@ -9269,16 +9269,16 @@
         <v>200</v>
       </c>
       <c r="D284" s="5">
-        <v>2213.87</v>
+        <v>2241.02</v>
       </c>
       <c r="E284" s="5">
         <v>0.49</v>
       </c>
       <c r="F284" s="5">
-        <v>2767.34</v>
+        <v>2801.27</v>
       </c>
       <c r="G284" s="5">
-        <v>3542.18</v>
+        <v>3585.63</v>
       </c>
       <c r="H284" s="6" t="s">
         <v>12</v>
@@ -9295,16 +9295,16 @@
         <v>200</v>
       </c>
       <c r="D285" s="5">
-        <v>1911.05</v>
+        <v>1858.05</v>
       </c>
       <c r="E285" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F285" s="5">
-        <v>2388.82</v>
+        <v>2322.56</v>
       </c>
       <c r="G285" s="5">
-        <v>3057.68</v>
+        <v>2972.88</v>
       </c>
       <c r="H285" s="6" t="s">
         <v>12</v>
@@ -9321,16 +9321,16 @@
         <v>200</v>
       </c>
       <c r="D286" s="5">
-        <v>1887.31</v>
+        <v>1863.84</v>
       </c>
       <c r="E286" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F286" s="5">
-        <v>2359.14</v>
+        <v>2329.8</v>
       </c>
       <c r="G286" s="5">
-        <v>3019.7</v>
+        <v>2982.15</v>
       </c>
       <c r="H286" s="6" t="s">
         <v>12</v>
@@ -9347,16 +9347,16 @@
         <v>200</v>
       </c>
       <c r="D287" s="5">
-        <v>1886.41</v>
+        <v>1898.59</v>
       </c>
       <c r="E287" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F287" s="5">
-        <v>2358.02</v>
+        <v>2373.23</v>
       </c>
       <c r="G287" s="5">
-        <v>3018.26</v>
+        <v>3037.74</v>
       </c>
       <c r="H287" s="6" t="s">
         <v>12</v>
@@ -9373,16 +9373,16 @@
         <v>200</v>
       </c>
       <c r="D288" s="5">
-        <v>1882.36</v>
+        <v>1924.62</v>
       </c>
       <c r="E288" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F288" s="5">
-        <v>2352.95</v>
+        <v>2405.77</v>
       </c>
       <c r="G288" s="5">
-        <v>3011.77</v>
+        <v>3079.39</v>
       </c>
       <c r="H288" s="6" t="s">
         <v>12</v>
@@ -9399,16 +9399,16 @@
         <v>200</v>
       </c>
       <c r="D289" s="5">
-        <v>1905.31</v>
+        <v>1912.9</v>
       </c>
       <c r="E289" s="5">
         <v>0.49</v>
       </c>
       <c r="F289" s="5">
-        <v>2381.64</v>
+        <v>2391.12</v>
       </c>
       <c r="G289" s="5">
-        <v>3048.5</v>
+        <v>3060.64</v>
       </c>
       <c r="H289" s="6" t="s">
         <v>12</v>
@@ -9425,16 +9425,16 @@
         <v>200</v>
       </c>
       <c r="D290" s="5">
-        <v>1953.65</v>
+        <v>1938.62</v>
       </c>
       <c r="E290" s="5">
         <v>0.49</v>
       </c>
       <c r="F290" s="5">
-        <v>2442.06</v>
+        <v>2423.27</v>
       </c>
       <c r="G290" s="5">
-        <v>3125.83</v>
+        <v>3101.79</v>
       </c>
       <c r="H290" s="6" t="s">
         <v>12</v>
@@ -9451,16 +9451,16 @@
         <v>200</v>
       </c>
       <c r="D291" s="5">
-        <v>1949.83</v>
+        <v>1973.74</v>
       </c>
       <c r="E291" s="5">
         <v>0.49</v>
       </c>
       <c r="F291" s="5">
-        <v>2437.29</v>
+        <v>2467.17</v>
       </c>
       <c r="G291" s="5">
-        <v>3119.72</v>
+        <v>3157.99</v>
       </c>
       <c r="H291" s="6" t="s">
         <v>12</v>
@@ -9477,16 +9477,16 @@
         <v>200</v>
       </c>
       <c r="D292" s="5">
-        <v>2059.69</v>
+        <v>2002.57</v>
       </c>
       <c r="E292" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F292" s="5">
-        <v>2574.61</v>
+        <v>2503.2</v>
       </c>
       <c r="G292" s="5">
-        <v>3295.5</v>
+        <v>3204.1</v>
       </c>
       <c r="H292" s="6" t="s">
         <v>12</v>
@@ -9503,16 +9503,16 @@
         <v>200</v>
       </c>
       <c r="D293" s="5">
-        <v>2032.49</v>
+        <v>2007.22</v>
       </c>
       <c r="E293" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F293" s="5">
-        <v>2540.61</v>
+        <v>2509.02</v>
       </c>
       <c r="G293" s="5">
-        <v>3251.98</v>
+        <v>3211.55</v>
       </c>
       <c r="H293" s="6" t="s">
         <v>12</v>
@@ -9529,16 +9529,16 @@
         <v>200</v>
       </c>
       <c r="D294" s="5">
-        <v>2029.95</v>
+        <v>2043.04</v>
       </c>
       <c r="E294" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F294" s="5">
-        <v>2537.43</v>
+        <v>2553.8</v>
       </c>
       <c r="G294" s="5">
-        <v>3247.91</v>
+        <v>3268.87</v>
       </c>
       <c r="H294" s="6" t="s">
         <v>12</v>
@@ -9555,16 +9555,16 @@
         <v>200</v>
       </c>
       <c r="D295" s="5">
-        <v>2024.04</v>
+        <v>2069.48</v>
       </c>
       <c r="E295" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F295" s="5">
-        <v>2530.05</v>
+        <v>2586.85</v>
       </c>
       <c r="G295" s="5">
-        <v>3238.46</v>
+        <v>3311.17</v>
       </c>
       <c r="H295" s="6" t="s">
         <v>12</v>
@@ -9581,16 +9581,16 @@
         <v>200</v>
       </c>
       <c r="D296" s="5">
-        <v>2047.2</v>
+        <v>2055.35</v>
       </c>
       <c r="E296" s="5">
         <v>0.49</v>
       </c>
       <c r="F296" s="5">
-        <v>2559</v>
+        <v>2569.19</v>
       </c>
       <c r="G296" s="5">
-        <v>3275.52</v>
+        <v>3288.56</v>
       </c>
       <c r="H296" s="6" t="s">
         <v>12</v>
@@ -9607,16 +9607,16 @@
         <v>200</v>
       </c>
       <c r="D297" s="5">
-        <v>2097.6</v>
+        <v>2081.46</v>
       </c>
       <c r="E297" s="5">
         <v>0.49</v>
       </c>
       <c r="F297" s="5">
-        <v>2622</v>
+        <v>2601.83</v>
       </c>
       <c r="G297" s="5">
-        <v>3356.16</v>
+        <v>3330.34</v>
       </c>
       <c r="H297" s="6" t="s">
         <v>12</v>
@@ -9633,16 +9633,16 @@
         <v>200</v>
       </c>
       <c r="D298" s="5">
-        <v>2092</v>
+        <v>2117.66</v>
       </c>
       <c r="E298" s="5">
         <v>0.49</v>
       </c>
       <c r="F298" s="5">
-        <v>2615.01</v>
+        <v>2647.07</v>
       </c>
       <c r="G298" s="5">
-        <v>3347.2</v>
+        <v>3388.26</v>
       </c>
       <c r="H298" s="6" t="s">
         <v>12</v>
@@ -9659,16 +9659,16 @@
         <v>200</v>
       </c>
       <c r="D299" s="5">
-        <v>2208.33</v>
+        <v>2147.08</v>
       </c>
       <c r="E299" s="5">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F299" s="5">
-        <v>2760.41</v>
+        <v>2683.84</v>
       </c>
       <c r="G299" s="5">
-        <v>3533.32</v>
+        <v>3435.33</v>
       </c>
       <c r="H299" s="6" t="s">
         <v>12</v>
@@ -9685,16 +9685,16 @@
         <v>200</v>
       </c>
       <c r="D300" s="5">
-        <v>2177.67</v>
+        <v>2150.59</v>
       </c>
       <c r="E300" s="5">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F300" s="5">
-        <v>2722.08</v>
+        <v>2688.23</v>
       </c>
       <c r="G300" s="5">
-        <v>3484.27</v>
+        <v>3440.94</v>
       </c>
       <c r="H300" s="6" t="s">
         <v>12</v>
@@ -9711,16 +9711,16 @@
         <v>200</v>
       </c>
       <c r="D301" s="5">
-        <v>2173.48</v>
+        <v>2187.5</v>
       </c>
       <c r="E301" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F301" s="5">
-        <v>2716.84</v>
+        <v>2734.38</v>
       </c>
       <c r="G301" s="5">
-        <v>3477.56</v>
+        <v>3500</v>
       </c>
       <c r="H301" s="6" t="s">
         <v>12</v>
@@ -9737,16 +9737,16 @@
         <v>200</v>
       </c>
       <c r="D302" s="5">
-        <v>2165.72</v>
+        <v>2214.34</v>
       </c>
       <c r="E302" s="5">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F302" s="5">
-        <v>2707.15</v>
+        <v>2767.93</v>
       </c>
       <c r="G302" s="5">
-        <v>3465.15</v>
+        <v>3542.95</v>
       </c>
       <c r="H302" s="6" t="s">
         <v>12</v>
@@ -9763,16 +9763,16 @@
         <v>200</v>
       </c>
       <c r="D303" s="5">
-        <v>2189.08</v>
+        <v>2197.8</v>
       </c>
       <c r="E303" s="5">
         <v>0.49</v>
       </c>
       <c r="F303" s="5">
-        <v>2736.35</v>
+        <v>2747.25</v>
       </c>
       <c r="G303" s="5">
-        <v>3502.54</v>
+        <v>3516.48</v>
       </c>
       <c r="H303" s="6" t="s">
         <v>12</v>
@@ -9789,16 +9789,16 @@
         <v>200</v>
       </c>
       <c r="D304" s="5">
-        <v>2241.55</v>
+        <v>2224.31</v>
       </c>
       <c r="E304" s="5">
         <v>0.49</v>
       </c>
       <c r="F304" s="5">
-        <v>2801.94</v>
+        <v>2780.38</v>
       </c>
       <c r="G304" s="5">
-        <v>3586.48</v>
+        <v>3558.89</v>
       </c>
       <c r="H304" s="6" t="s">
         <v>12</v>
